--- a/marketing/auditorias-seo/auditoria-site-consolidada-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/auditoria-site-consolidada-2026-09-25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F20688D-1B5B-43B1-807C-0621103C5FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A72556D2-3B1B-4753-A654-C714B075ABD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C7F21A3-C379-462A-AA44-89C0CB959446}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0BEFFF4A-346F-4456-8A5C-ED58C33935F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Painel" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Varredura 91 URLs" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plano de ação'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plano de ação'!$A$1:$J$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Varredura 91 URLs'!$A$1:$K$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="568">
   <si>
     <t>Prioridade</t>
   </si>
@@ -87,78 +87,144 @@
     <t>Site todo</t>
   </si>
   <si>
+    <t>Backup</t>
+  </si>
+  <si>
+    <t>Hostinger faz backup automático diário; backup manual criado em 25/09 antes das mudanças</t>
+  </si>
+  <si>
+    <t>hPanel &gt; Sites &gt; solveplan.com &gt; Arquivos &gt; Backups</t>
+  </si>
+  <si>
+    <t>Risco</t>
+  </si>
+  <si>
+    <t>Fácil</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Análise site 25/09</t>
+  </si>
+  <si>
+    <t>Instalar Wordfence</t>
+  </si>
+  <si>
+    <t>Instalado e ativado (9.0.1) em 25/09 com licença gratuita; firewall em modo básico. Não otimizar firewall por enquanto (mexe em .htaccess)</t>
+  </si>
+  <si>
+    <t>Plugins</t>
+  </si>
+  <si>
     <t>Desativar xmlrpc.php</t>
   </si>
   <si>
     <t>Endpoint aberto (responde 200), vetor de força bruta</t>
   </si>
   <si>
-    <t>Wordfence &gt; Firewall ou regra no .htaccess via hospedagem</t>
-  </si>
-  <si>
-    <t>Risco</t>
-  </si>
-  <si>
-    <t>Fácil</t>
+    <t>Feito 25/09: Wordfence &gt; Segurança de acesso &gt; Configurações &gt; Desativar a autenticação XML-RPC</t>
+  </si>
+  <si>
+    <t>Revogar Application Password</t>
+  </si>
+  <si>
+    <t>A senha do usuário administrador foi compartilhada no chat. Revogar e criar outra só quando precisar</t>
+  </si>
+  <si>
+    <t>Usuários &gt; administrador &gt; Senhas de aplicativo &gt; Revogar</t>
+  </si>
+  <si>
+    <t>Bloquear listagem pública de usuários</t>
+  </si>
+  <si>
+    <t>/wp-json/wp/v2/users expõe os logins administrador, felippeemanoel e solveplan</t>
+  </si>
+  <si>
+    <t>Feito 25/09: Wordfence &gt; Todas as opções &gt; Brute Force &gt; Prevent discovery of usernames (testado: /users = 401, ?author = 404)</t>
+  </si>
+  <si>
+    <t>2-Alta</t>
+  </si>
+  <si>
+    <t>SEO técnico</t>
+  </si>
+  <si>
+    <t>Todas as páginas</t>
+  </si>
+  <si>
+    <t>Schema errado (BlogPosting + Person)</t>
+  </si>
+  <si>
+    <t>Páginas saem como artigo, com o usuário felippeemanoel como autor</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Títulos e Meta &gt; Páginas &gt; Tipo de Schema: Nenhum/WebPage</t>
+  </si>
+  <si>
+    <t>GEO +1-2/pág</t>
   </si>
   <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>Análise site 25/09</t>
-  </si>
-  <si>
-    <t>Backup</t>
-  </si>
-  <si>
-    <t>Nenhum plugin de backup visível. Confirmar backup diário com a hospedagem ou instalar UpdraftPlus</t>
-  </si>
-  <si>
-    <t>Hospedagem / Plugins &gt; Adicionar novo</t>
-  </si>
-  <si>
-    <t>Revogar Application Password</t>
-  </si>
-  <si>
-    <t>A senha do usuário administrador foi compartilhada no chat. Revogar e criar outra só quando precisar</t>
-  </si>
-  <si>
-    <t>Usuários &gt; administrador &gt; Senhas de aplicativo &gt; Revogar</t>
-  </si>
-  <si>
-    <t>Bloquear listagem pública de usuários</t>
-  </si>
-  <si>
-    <t>/wp-json/wp/v2/users expõe os logins administrador, felippeemanoel e solveplan</t>
-  </si>
-  <si>
-    <t>Plugin de segurança (Wordfence) ou regra no LiteSpeed</t>
-  </si>
-  <si>
-    <t>2-Alta</t>
-  </si>
-  <si>
-    <t>SEO técnico</t>
-  </si>
-  <si>
-    <t>Todas as páginas</t>
-  </si>
-  <si>
-    <t>Schema errado (BlogPosting + Person)</t>
-  </si>
-  <si>
-    <t>Páginas saem como artigo, com o usuário felippeemanoel como autor</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Títulos e Meta &gt; Páginas &gt; Tipo de Schema: Nenhum/WebPage</t>
-  </si>
-  <si>
-    <t>GEO +1-2/pág</t>
-  </si>
-  <si>
     <t>Auditoria 28/07 + 30/07 + 25/09</t>
   </si>
   <si>
+    <t>28 páginas institucionais</t>
+  </si>
+  <si>
+    <t>Adicionar H1</t>
+  </si>
+  <si>
+    <t>Home, BDC, serviços, contato, sobre e todos os aceleradores estão sem H1. Modelo: /sap-datasphere/</t>
+  </si>
+  <si>
+    <t>Elementor &gt; widget Título principal &gt; Tag HTML: H1</t>
+  </si>
+  <si>
+    <t>SEO +7/pág</t>
+  </si>
+  <si>
+    <t>Auditoria 28/07 + 25/09</t>
+  </si>
+  <si>
+    <t>Conversão</t>
+  </si>
+  <si>
+    <t>/contato/</t>
+  </si>
+  <si>
+    <t>Melhorar página de contato</t>
+  </si>
+  <si>
+    <t>Corrigir o horário ("8h-18h e 13h-18h30"), dizer o próximo passo depois do envio, incluir agendamento HubSpot Meetings e H1</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Contato</t>
+  </si>
+  <si>
+    <t>Pipeline</t>
+  </si>
+  <si>
+    <t>Nova página</t>
+  </si>
+  <si>
+    <t>Landing page BDC para ads</t>
+  </si>
+  <si>
+    <t>LP dedicada para LinkedIn e Google Ads (prioridade H2 2026)</t>
+  </si>
+  <si>
+    <t>Elementor &gt; nova página (noindex se for só para mídia)</t>
+  </si>
+  <si>
+    <t>Médio</t>
+  </si>
+  <si>
+    <t>Análise site 25/09 / estratégia H2</t>
+  </si>
+  <si>
     <t>AEO</t>
   </si>
   <si>
@@ -177,51 +243,9 @@
     <t>+10 (+7 perguntas nos headings)</t>
   </si>
   <si>
-    <t>Médio</t>
-  </si>
-  <si>
     <t>Auditoria home 25/09</t>
   </si>
   <si>
-    <t>Conversão</t>
-  </si>
-  <si>
-    <t>Nova página</t>
-  </si>
-  <si>
-    <t>Landing page BDC para ads</t>
-  </si>
-  <si>
-    <t>LP dedicada para LinkedIn e Google Ads (prioridade H2 2026)</t>
-  </si>
-  <si>
-    <t>Elementor &gt; nova página (noindex se for só para mídia)</t>
-  </si>
-  <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
-    <t>Análise site 25/09 / estratégia H2</t>
-  </si>
-  <si>
-    <t>28 páginas institucionais</t>
-  </si>
-  <si>
-    <t>Adicionar H1</t>
-  </si>
-  <si>
-    <t>Home, BDC, serviços, contato, sobre e todos os aceleradores estão sem H1. Modelo: /sap-datasphere/</t>
-  </si>
-  <si>
-    <t>Elementor &gt; widget Título principal &gt; Tag HTML: H1</t>
-  </si>
-  <si>
-    <t>SEO +7/pág</t>
-  </si>
-  <si>
-    <t>Auditoria 28/07 + 25/09</t>
-  </si>
-  <si>
     <t>SEO página</t>
   </si>
   <si>
@@ -246,7 +270,7 @@
     <t>Bloco de snippet</t>
   </si>
   <si>
-    <t>H2 "O que a Solveplan faz?" + parágrafo de 54 palavras (texto no relatório site-2026-09-25-analise.md)</t>
+    <t>H2 "O que a Solveplan faz?" + parágrafo de 54 palavras (texto no relatório site-2026-09-25-analise.md; trocar 390 por 300 projetos)</t>
   </si>
   <si>
     <t>Elementor &gt; Título H2 + Editor de texto</t>
@@ -261,138 +285,123 @@
     <t>Rank Math &gt; Editar snippet &gt; Descrição</t>
   </si>
   <si>
+    <t>Hero focado em BDC</t>
+  </si>
+  <si>
+    <t>Hero com SAP BDC + selo Melhor Parceiro SAP BDC 2026 LATAM + CTA "Agende um diagnóstico BDC"</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Home &gt; seção hero</t>
+  </si>
+  <si>
+    <t>/sap-business-data-cloud/</t>
+  </si>
+  <si>
+    <t>Reescrever página BDC</t>
+  </si>
+  <si>
+    <t>65% do tráfego, 302 palavras genéricas, sem case, sem FAQ, 1 CTA. Estrutura: dor &gt; abordagem Solveplan &gt; case &gt; FAQ &gt; CTA (usar /pagina-solucao)</t>
+  </si>
+  <si>
+    <t>Elementor &gt; página BDC</t>
+  </si>
+  <si>
+    <t>Difícil</t>
+  </si>
+  <si>
+    <t>Faixa de prova social</t>
+  </si>
+  <si>
+    <t>Prêmio 2026, prêmio 2025, SAP Gold e logos de clientes logo abaixo do hero</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Home</t>
+  </si>
+  <si>
+    <t>Title e description da BDC</t>
+  </si>
+  <si>
+    <t>Title: "Consultoria SAP Business Data Cloud (BDC) | Solveplan". Description: "Implemente SAP Business Data Cloud com o Melhor Parceiro SAP BDC 2026 da América Latina. Unifique dados SAP e não-SAP para analytics e IA."</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Editar snippet</t>
+  </si>
+  <si>
+    <t>SEO</t>
+  </si>
+  <si>
+    <t>Contadores legíveis por robôs</t>
+  </si>
+  <si>
+    <t>O HTML entrega "0+" (a animação só roda com JavaScript). Pôr o número real como texto</t>
+  </si>
+  <si>
+    <t>Elementor &gt; widget Contador &gt; valor inicial = valor final, ou widget Título</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>CTA quebrado</t>
+  </si>
+  <si>
+    <t>"Fale com nossos especialistas" leva para /aceleradores/. Apontar para /contato/ ou para a LP BDC</t>
+  </si>
+  <si>
+    <t>Elementor &gt; botão &gt; Link</t>
+  </si>
+  <si>
+    <t>Post BW/4HANA</t>
+  </si>
+  <si>
+    <t>FAQ com schema</t>
+  </si>
+  <si>
+    <t>A seção FAQ existe, mas falta o schema FAQPage</t>
+  </si>
+  <si>
+    <t>Rank Math Schema Generator ou widget HTML</t>
+  </si>
+  <si>
+    <t>Parcial</t>
+  </si>
+  <si>
+    <t>Auditoria BW/4HANA 17/09</t>
+  </si>
+  <si>
+    <t>/sap-datasphere/</t>
+  </si>
+  <si>
+    <t>A seção "Perguntas frequentes" existe, mas falta o schema FAQPage</t>
+  </si>
+  <si>
+    <t>Widget HTML com JSON-LD FAQPage</t>
+  </si>
+  <si>
+    <t>Auditoria Datasphere 30/07</t>
+  </si>
+  <si>
+    <t>Meta description, title e slug</t>
+  </si>
+  <si>
+    <t>Publicado com title de 57 caracteres, description e slug /blog/sap-datasphere-x-sap-bw4hana/</t>
+  </si>
+  <si>
+    <t>Rank Math / permalink</t>
+  </si>
+  <si>
     <t>Confirmar números oficiais</t>
   </si>
   <si>
     <t>Site: 150+ empresas / 300+ projetos / 68+ especialistas. Contexto interno: 150+ / 390+ / 60+. Definir o oficial e atualizar</t>
   </si>
   <si>
-    <t>Elementor &gt; widgets Contador (home)</t>
+    <t>Definido em 25/09: oficiais são os do site (150+ / 300+ / 68+ / 13+). Manter contadores</t>
   </si>
   <si>
     <t>Credibilidade</t>
   </si>
   <si>
-    <t>Hero focado em BDC</t>
-  </si>
-  <si>
-    <t>Hero com SAP BDC + selo Melhor Parceiro SAP BDC 2026 LATAM + CTA "Agende um diagnóstico BDC"</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Home &gt; seção hero</t>
-  </si>
-  <si>
-    <t>/sap-business-data-cloud/</t>
-  </si>
-  <si>
-    <t>Title e description da BDC</t>
-  </si>
-  <si>
-    <t>Title: "Consultoria SAP Business Data Cloud (BDC) | Solveplan". Description: "Implemente SAP Business Data Cloud com o Melhor Parceiro SAP BDC 2026 da América Latina. Unifique dados SAP e não-SAP para analytics e IA."</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Editar snippet</t>
-  </si>
-  <si>
-    <t>SEO</t>
-  </si>
-  <si>
-    <t>Faixa de prova social</t>
-  </si>
-  <si>
-    <t>Prêmio 2026, prêmio 2025, SAP Gold e logos de clientes logo abaixo do hero</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Home</t>
-  </si>
-  <si>
-    <t>Reescrever página BDC</t>
-  </si>
-  <si>
-    <t>65% do tráfego, 302 palavras genéricas, sem case, sem FAQ, 1 CTA. Estrutura: dor &gt; abordagem Solveplan &gt; case &gt; FAQ &gt; CTA (usar /pagina-solucao)</t>
-  </si>
-  <si>
-    <t>Elementor &gt; página BDC</t>
-  </si>
-  <si>
-    <t>Difícil</t>
-  </si>
-  <si>
-    <t>CTA quebrado</t>
-  </si>
-  <si>
-    <t>"Fale com nossos especialistas" leva para /aceleradores/. Apontar para /contato/ ou para a LP BDC</t>
-  </si>
-  <si>
-    <t>Elementor &gt; botão &gt; Link</t>
-  </si>
-  <si>
-    <t>Contadores legíveis por robôs</t>
-  </si>
-  <si>
-    <t>O HTML entrega "0+" (a animação só roda com JavaScript). Pôr o número real como texto</t>
-  </si>
-  <si>
-    <t>Elementor &gt; widget Contador &gt; valor inicial = valor final, ou widget Título</t>
-  </si>
-  <si>
-    <t>GEO</t>
-  </si>
-  <si>
-    <t>/contato/</t>
-  </si>
-  <si>
-    <t>Melhorar página de contato</t>
-  </si>
-  <si>
-    <t>Corrigir o horário ("8h-18h e 13h-18h30"), dizer o próximo passo depois do envio, incluir agendamento HubSpot Meetings e H1</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Contato</t>
-  </si>
-  <si>
-    <t>Post BW/4HANA</t>
-  </si>
-  <si>
-    <t>FAQ com schema</t>
-  </si>
-  <si>
-    <t>A seção FAQ existe, mas falta o schema FAQPage</t>
-  </si>
-  <si>
-    <t>Rank Math Schema Generator ou widget HTML</t>
-  </si>
-  <si>
-    <t>Parcial</t>
-  </si>
-  <si>
-    <t>Auditoria BW/4HANA 17/09</t>
-  </si>
-  <si>
-    <t>/sap-datasphere/</t>
-  </si>
-  <si>
-    <t>A seção "Perguntas frequentes" existe, mas falta o schema FAQPage</t>
-  </si>
-  <si>
-    <t>Widget HTML com JSON-LD FAQPage</t>
-  </si>
-  <si>
-    <t>Auditoria Datasphere 30/07</t>
-  </si>
-  <si>
-    <t>Meta description, title e slug</t>
-  </si>
-  <si>
-    <t>Publicado com title de 57 caracteres, description e slug /blog/sap-datasphere-x-sap-bw4hana/</t>
-  </si>
-  <si>
-    <t>Rank Math / permalink</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
     <t>Headings em pergunta + snippet</t>
   </si>
   <si>
@@ -429,6 +438,15 @@
     <t>Elementor &gt; seção Sobre</t>
   </si>
   <si>
+    <t>Post Clean Core</t>
+  </si>
+  <si>
+    <t>Description copiada errada</t>
+  </si>
+  <si>
+    <t>Usa a description do post de agronegócio</t>
+  </si>
+  <si>
     <t>Páginas de solução</t>
   </si>
   <si>
@@ -471,6 +489,39 @@
     <t>Rank Math &gt; Títulos e Meta &gt; cada tipo de post &gt; noindex e remover do sitemap</t>
   </si>
   <si>
+    <t>Atualizar WordPress 6.8.9 &gt; 7.1.2</t>
+  </si>
+  <si>
+    <t>Salto grande de versão: fazer com backup e testar Elementor antes (idealmente em staging da Hostinger)</t>
+  </si>
+  <si>
+    <t>Painel &gt; Atualizações</t>
+  </si>
+  <si>
+    <t>Sessão 25/09</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Home, BDC, Datasphere, BW/4HANA</t>
+  </si>
+  <si>
+    <t>Medir PageSpeed</t>
+  </si>
+  <si>
+    <t>A cota da API estava esgotada em todas as auditorias. Rodar mobile e desktop e registrar LCP/CLS</t>
+  </si>
+  <si>
+    <t>pagespeed.web.dev</t>
+  </si>
+  <si>
+    <t>até +20/pág</t>
+  </si>
+  <si>
+    <t>Todas as auditorias</t>
+  </si>
+  <si>
     <t>Contato, Sobre, Analytics, Blog, Serviços</t>
   </si>
   <si>
@@ -492,36 +543,6 @@
     <t>Posts + Rank Math &gt; Redirecionamentos</t>
   </si>
   <si>
-    <t>Post Clean Core</t>
-  </si>
-  <si>
-    <t>Description copiada errada</t>
-  </si>
-  <si>
-    <t>Usa a description do post de agronegócio</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Home, BDC, Datasphere, BW/4HANA</t>
-  </si>
-  <si>
-    <t>Medir PageSpeed</t>
-  </si>
-  <si>
-    <t>A cota da API estava esgotada em todas as auditorias. Rodar mobile e desktop e registrar LCP/CLS</t>
-  </si>
-  <si>
-    <t>pagespeed.web.dev</t>
-  </si>
-  <si>
-    <t>até +20/pág</t>
-  </si>
-  <si>
-    <t>Todas as auditorias</t>
-  </si>
-  <si>
     <t>Alts de imagens</t>
   </si>
   <si>
@@ -567,6 +588,15 @@
     <t>4-Baixa</t>
   </si>
   <si>
+    <t>Ativar 2FA para administradores</t>
+  </si>
+  <si>
+    <t>Opcional; muda a forma de login no painel</t>
+  </si>
+  <si>
+    <t>Wordfence &gt; Segurança de acesso &gt; Configurações &gt; 2FA</t>
+  </si>
+  <si>
     <t>Headings H5 para H2</t>
   </si>
   <si>
@@ -585,6 +615,18 @@
     <t>Image Optimization &gt; Configurações &gt; WebP</t>
   </si>
   <si>
+    <t>Conteúdo</t>
+  </si>
+  <si>
+    <t>Erros de digitação</t>
+  </si>
+  <si>
+    <t>Menu "Analitycs", rodapé "SAP DataSphere", "SolvePlan" x "Solveplan" nas notícias</t>
+  </si>
+  <si>
+    <t>Aparência &gt; Menus / Elementor rodapé / notícias</t>
+  </si>
+  <si>
     <t>og:image</t>
   </si>
   <si>
@@ -597,18 +639,6 @@
     <t>Social</t>
   </si>
   <si>
-    <t>Conteúdo</t>
-  </si>
-  <si>
-    <t>Erros de digitação</t>
-  </si>
-  <si>
-    <t>Menu "Analitycs", rodapé "SAP DataSphere", "SolvePlan" x "Solveplan" nas notícias</t>
-  </si>
-  <si>
-    <t>Aparência &gt; Menus / Elementor rodapé / notícias</t>
-  </si>
-  <si>
     <t>Links internos no corpo</t>
   </si>
   <si>
@@ -1584,7 +1614,7 @@
     <t>Auditoria consolidada — solveplan.com</t>
   </si>
   <si>
-    <t>Consolida as auditorias de 28/07 (site), 30/07 (Datasphere), 17/09 (BW/4HANA) e 25/09 (home + varredura de 91 URLs). Atualizado em 25/09/2026.</t>
+    <t>Consolida as auditorias de 28/07 (site), 30/07 (Datasphere), 17/09 (BW/4HANA) e 25/09 (home + varredura de 91 URLs). Atualizado em 25/09/2026 (segurança concluída).</t>
   </si>
   <si>
     <t>Diagnóstico em uma frase</t>
@@ -1671,13 +1701,10 @@
     <t>Por quê</t>
   </si>
   <si>
-    <t>Revogar a Application Password; bloquear a listagem de usuários e o xmlrpc</t>
-  </si>
-  <si>
-    <t>Hoje</t>
-  </si>
-  <si>
-    <t>Risco de segurança aberto</t>
+    <t>CONCLUÍDO 25/09: Wordfence, bloqueio de usuários e xmlrpc, backup</t>
+  </si>
+  <si>
+    <t>Frente de segurança fechada</t>
   </si>
   <si>
     <t>H1 + schema + noindex do lixo + titles/descriptions no site todo</t>
@@ -1793,6 +1820,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9F7DA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1800,12 +1833,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9F7DA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1869,13 +1896,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2225,7 +2252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{786E9ACD-A5B2-42DD-956A-39F058F0835D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E0B5BF-A688-4A60-9E65-75974B332389}">
   <dimension ref="B1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2237,7 +2264,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="22" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -2245,7 +2272,7 @@
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="23" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -2253,7 +2280,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="24" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -2261,7 +2288,7 @@
     </row>
     <row r="5" spans="2:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="15" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -2269,21 +2296,21 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="C8" s="25">
         <v>30</v>
@@ -2292,12 +2319,12 @@
         <v>28</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="C9" s="25">
         <v>84</v>
@@ -2306,85 +2333,85 @@
         <v>91</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="D10" s="25">
         <v>26</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="C11" s="25">
         <v>30</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>18</v>
+      <c r="B16" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="C16" s="17">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C17" s="17">
@@ -2393,115 +2420,115 @@
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="5" t="s">
-        <v>114</v>
+      <c r="B19" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C19" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="C20" s="26">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>542</v>
+        <v>18</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="7" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="7" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="7" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="7" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="7" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="7" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="15" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
@@ -2526,8 +2553,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBCA72E-067D-425E-A07C-5FEC842924EA}">
-  <dimension ref="A1:J45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65ABC09B-8826-4137-BD33-1F4E1F877729}">
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -2701,27 +2728,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>34</v>
-      </c>
       <c r="G6" s="9" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>17</v>
@@ -2730,306 +2757,306 @@
         <v>18</v>
       </c>
       <c r="J6" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="F7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="H7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>40</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="H8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>18</v>
+      <c r="I9" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J9" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="I10" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="9" t="s">
+    </row>
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="C11" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="D11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="9">
+      <c r="E11" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="9">
         <v>8</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="9">
-        <v>7</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="9">
-        <v>10</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>18</v>
+      <c r="I12" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="10" t="s">
-        <v>18</v>
+      <c r="I13" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="G14" s="9">
+        <v>10</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>18</v>
+      <c r="I14" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>50</v>
+        <v>78</v>
+      </c>
+      <c r="G15" s="9">
+        <v>3</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>79</v>
@@ -3041,27 +3068,27 @@
         <v>81</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>18</v>
+        <v>57</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>83</v>
@@ -3073,59 +3100,59 @@
         <v>85</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>18</v>
+        <v>86</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>90</v>
@@ -3137,13 +3164,13 @@
         <v>92</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>18</v>
+      <c r="I19" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>19</v>
@@ -3151,31 +3178,31 @@
     </row>
     <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="10" t="s">
-        <v>18</v>
+      <c r="I20" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>19</v>
@@ -3183,13 +3210,13 @@
     </row>
     <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>98</v>
@@ -3201,13 +3228,13 @@
         <v>100</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="10" t="s">
-        <v>18</v>
+      <c r="I21" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>19</v>
@@ -3215,10 +3242,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>101</v>
@@ -3236,9 +3263,9 @@
         <v>2</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>105</v>
       </c>
       <c r="J22" s="9" t="s">
@@ -3247,10 +3274,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>107</v>
@@ -3268,9 +3295,9 @@
         <v>2</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="12" t="s">
         <v>105</v>
       </c>
       <c r="J23" s="9" t="s">
@@ -3279,10 +3306,10 @@
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>101</v>
@@ -3302,51 +3329,51 @@
       <c r="H24" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="12" t="s">
-        <v>114</v>
+      <c r="I24" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="G25" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="G25" s="9">
-        <v>11</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>114</v>
+      <c r="I25" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>107</v>
@@ -3361,13 +3388,13 @@
         <v>120</v>
       </c>
       <c r="G26" s="9">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="12" t="s">
-        <v>114</v>
+      <c r="I26" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>110</v>
@@ -3375,10 +3402,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>107</v>
@@ -3390,16 +3417,16 @@
         <v>122</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G27" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="12" t="s">
-        <v>114</v>
+      <c r="I27" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>110</v>
@@ -3407,13 +3434,13 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>124</v>
@@ -3422,10 +3449,10 @@
         <v>125</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G28" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>17</v>
@@ -3434,47 +3461,47 @@
         <v>18</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C29" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="E29" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>82</v>
+      <c r="G29" s="9">
+        <v>2</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="10" t="s">
-        <v>18</v>
+      <c r="I29" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>130</v>
@@ -3486,30 +3513,30 @@
         <v>132</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>18</v>
+      <c r="I30" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>134</v>
@@ -3518,80 +3545,80 @@
         <v>135</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="10" t="s">
-        <v>18</v>
+      <c r="I31" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="F32" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>140</v>
-      </c>
       <c r="G32" s="9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>18</v>
+      <c r="I32" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="F33" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>81</v>
-      </c>
       <c r="G33" s="9" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>18</v>
+      <c r="I33" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>19</v>
@@ -3599,71 +3626,71 @@
     </row>
     <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="F34" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="G34" s="9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="F35" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="G35" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>151</v>
@@ -3686,8 +3713,8 @@
       <c r="H36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="10" t="s">
-        <v>18</v>
+      <c r="I36" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>157</v>
@@ -3695,153 +3722,153 @@
     </row>
     <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>12</v>
+        <v>158</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="10" t="s">
-        <v>18</v>
+      <c r="I37" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J37" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="9" t="s">
+      <c r="E38" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="F38" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="G38" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="G38" s="9">
-        <v>1</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="13" t="s">
+      <c r="E39" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="J38" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" s="9" t="s">
+      <c r="F39" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="G39" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G39" s="9">
-        <v>3</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>114</v>
+      <c r="I39" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G40" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="12" t="s">
-        <v>114</v>
+      <c r="I40" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="G41" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>17</v>
@@ -3850,18 +3877,18 @@
         <v>18</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>176</v>
@@ -3872,8 +3899,8 @@
       <c r="F42" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="G42" s="9" t="s">
-        <v>151</v>
+      <c r="G42" s="9">
+        <v>6</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>17</v>
@@ -3882,113 +3909,209 @@
         <v>18</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="H43" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="10" t="s">
-        <v>18</v>
+      <c r="I43" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>19</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B44" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="9" t="s">
+      <c r="E44" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="F44" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>74</v>
+      <c r="G44" s="9">
+        <v>1</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I44" s="10" t="s">
-        <v>18</v>
+      <c r="I44" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>58</v>
+        <v>151</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="F45" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F45" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G45" s="9">
-        <v>1</v>
+      <c r="G45" s="9" t="s">
+        <v>151</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="13" t="s">
-        <v>166</v>
+      <c r="I45" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J45" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="G48" s="9">
+        <v>1</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="J48" s="9" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J45" xr:uid="{1BBCA72E-067D-425E-A07C-5FEC842924EA}"/>
+  <autoFilter ref="A1:J48" xr:uid="{65ABC09B-8826-4137-BD33-1F4E1F877729}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{266E3D2A-5A26-4840-8E04-B730F2EE2560}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C942FDC-0ABF-4656-9439-8CB43AD7A5A2}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4001,30 +4124,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C2" s="17">
         <v>10</v>
@@ -4041,10 +4164,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C3" s="17">
         <v>10</v>
@@ -4061,10 +4184,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C4" s="17">
         <v>10</v>
@@ -4081,10 +4204,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C5" s="17">
         <v>10</v>
@@ -4104,7 +4227,7 @@
         <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C6" s="17">
         <v>8</v>
@@ -4124,7 +4247,7 @@
         <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C7" s="17">
         <v>5</v>
@@ -4144,7 +4267,7 @@
         <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C8" s="17">
         <v>4</v>
@@ -4164,7 +4287,7 @@
         <v>151</v>
       </c>
       <c r="B9" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C9" s="17">
         <v>3</v>
@@ -4181,10 +4304,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C10" s="17">
         <v>10</v>
@@ -4201,10 +4324,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C11" s="17">
         <v>8</v>
@@ -4221,10 +4344,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C12" s="17">
         <v>7</v>
@@ -4241,10 +4364,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C13" s="17">
         <v>6</v>
@@ -4261,10 +4384,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C14" s="17">
         <v>5</v>
@@ -4281,10 +4404,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C15" s="17">
         <v>4</v>
@@ -4301,7 +4424,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="21">
@@ -4323,7 +4446,7 @@
     </row>
     <row r="18" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -4340,7 +4463,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEEC501-A461-4B01-A803-6C078EA74428}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662A7064-CBB1-4153-A2CE-0F17B0896B3E}">
   <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4358,47 +4481,47 @@
   <sheetData>
     <row r="1" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C2" s="3">
+        <v>231</v>
+      </c>
+      <c r="C2" s="4">
         <v>0</v>
       </c>
       <c r="D2">
@@ -4414,24 +4537,24 @@
         <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="I2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="J2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -4449,23 +4572,23 @@
         <v>156</v>
       </c>
       <c r="H3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="I3" t="s">
-        <v>228</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>229</v>
+        <v>238</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" s="3">
+        <v>240</v>
+      </c>
+      <c r="C4" s="4">
         <v>0</v>
       </c>
       <c r="D4">
@@ -4481,26 +4604,26 @@
         <v>188</v>
       </c>
       <c r="H4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="I4" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="J4" t="s">
-        <v>233</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>225</v>
+        <v>243</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="3">
+        <v>244</v>
+      </c>
+      <c r="C5" s="4">
         <v>0</v>
       </c>
       <c r="D5">
@@ -4516,26 +4639,26 @@
         <v>158</v>
       </c>
       <c r="H5" t="s">
+        <v>245</v>
+      </c>
+      <c r="I5" t="s">
+        <v>246</v>
+      </c>
+      <c r="J5" t="s">
+        <v>234</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="I5" t="s">
-        <v>236</v>
-      </c>
-      <c r="J5" t="s">
-        <v>224</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" s="3">
+        <v>247</v>
+      </c>
+      <c r="C6" s="4">
         <v>0</v>
       </c>
       <c r="D6">
@@ -4551,26 +4674,26 @@
         <v>156</v>
       </c>
       <c r="H6" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="I6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="J6" t="s">
-        <v>240</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B7" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" s="3">
+        <v>251</v>
+      </c>
+      <c r="C7" s="4">
         <v>0</v>
       </c>
       <c r="D7">
@@ -4586,26 +4709,26 @@
         <v>98</v>
       </c>
       <c r="H7" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="I7" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="J7" t="s">
-        <v>244</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>225</v>
+        <v>254</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C8" s="3">
+        <v>255</v>
+      </c>
+      <c r="C8" s="4">
         <v>0</v>
       </c>
       <c r="D8">
@@ -4621,26 +4744,26 @@
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="I8" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="J8" t="s">
-        <v>224</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C9" s="3">
+        <v>258</v>
+      </c>
+      <c r="C9" s="4">
         <v>0</v>
       </c>
       <c r="D9">
@@ -4656,26 +4779,26 @@
         <v>155</v>
       </c>
       <c r="H9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="I9" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="J9" t="s">
-        <v>251</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C10" s="3">
+        <v>262</v>
+      </c>
+      <c r="C10" s="4">
         <v>0</v>
       </c>
       <c r="D10">
@@ -4691,26 +4814,26 @@
         <v>147</v>
       </c>
       <c r="H10" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I10" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="J10" t="s">
-        <v>240</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B11" t="s">
-        <v>255</v>
-      </c>
-      <c r="C11" s="3">
+        <v>265</v>
+      </c>
+      <c r="C11" s="4">
         <v>0</v>
       </c>
       <c r="D11">
@@ -4726,26 +4849,26 @@
         <v>155</v>
       </c>
       <c r="H11" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="I11" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="J11" t="s">
-        <v>244</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>225</v>
+        <v>254</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
-      </c>
-      <c r="C12" s="3">
+        <v>268</v>
+      </c>
+      <c r="C12" s="4">
         <v>0</v>
       </c>
       <c r="D12">
@@ -4761,26 +4884,26 @@
         <v>158</v>
       </c>
       <c r="H12" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="I12" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="J12" t="s">
-        <v>244</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>225</v>
+        <v>254</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B13" t="s">
-        <v>260</v>
-      </c>
-      <c r="C13" s="3">
+        <v>270</v>
+      </c>
+      <c r="C13" s="4">
         <v>0</v>
       </c>
       <c r="D13">
@@ -4796,26 +4919,26 @@
         <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="I13" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="J13" t="s">
-        <v>224</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
-      </c>
-      <c r="C14" s="3">
+        <v>273</v>
+      </c>
+      <c r="C14" s="4">
         <v>0</v>
       </c>
       <c r="D14">
@@ -4831,26 +4954,26 @@
         <v>154</v>
       </c>
       <c r="H14" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="I14" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="J14" t="s">
-        <v>251</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B15" t="s">
-        <v>266</v>
-      </c>
-      <c r="C15" s="3">
+        <v>276</v>
+      </c>
+      <c r="C15" s="4">
         <v>0</v>
       </c>
       <c r="D15">
@@ -4866,26 +4989,26 @@
         <v>154</v>
       </c>
       <c r="H15" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="I15" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="J15" t="s">
-        <v>251</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B16" t="s">
-        <v>269</v>
-      </c>
-      <c r="C16" s="3">
+        <v>279</v>
+      </c>
+      <c r="C16" s="4">
         <v>0</v>
       </c>
       <c r="D16">
@@ -4901,26 +5024,26 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="I16" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="J16" t="s">
-        <v>224</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B17" t="s">
-        <v>272</v>
-      </c>
-      <c r="C17" s="3">
+        <v>282</v>
+      </c>
+      <c r="C17" s="4">
         <v>0</v>
       </c>
       <c r="D17">
@@ -4936,26 +5059,26 @@
         <v>156</v>
       </c>
       <c r="H17" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="I17" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="J17" t="s">
-        <v>244</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>225</v>
+        <v>254</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B18" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18" s="3">
+        <v>285</v>
+      </c>
+      <c r="C18" s="4">
         <v>0</v>
       </c>
       <c r="D18">
@@ -4971,26 +5094,26 @@
         <v>157</v>
       </c>
       <c r="H18" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="I18" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="J18" t="s">
-        <v>251</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s">
-        <v>278</v>
-      </c>
-      <c r="C19" s="3">
+        <v>288</v>
+      </c>
+      <c r="C19" s="4">
         <v>0</v>
       </c>
       <c r="D19">
@@ -5006,26 +5129,26 @@
         <v>156</v>
       </c>
       <c r="H19" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="I19" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="J19" t="s">
-        <v>224</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s">
-        <v>281</v>
-      </c>
-      <c r="C20" s="3">
+        <v>291</v>
+      </c>
+      <c r="C20" s="4">
         <v>0</v>
       </c>
       <c r="D20">
@@ -5041,26 +5164,26 @@
         <v>157</v>
       </c>
       <c r="H20" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="I20" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="J20" t="s">
-        <v>224</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
-      </c>
-      <c r="C21" s="3">
+        <v>294</v>
+      </c>
+      <c r="C21" s="4">
         <v>0</v>
       </c>
       <c r="D21">
@@ -5076,26 +5199,26 @@
         <v>154</v>
       </c>
       <c r="H21" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="I21" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="J21" t="s">
-        <v>251</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="3">
+        <v>297</v>
+      </c>
+      <c r="C22" s="4">
         <v>0</v>
       </c>
       <c r="D22">
@@ -5111,26 +5234,26 @@
         <v>156</v>
       </c>
       <c r="H22" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="I22" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="J22" t="s">
-        <v>244</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>225</v>
+        <v>254</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s">
-        <v>290</v>
-      </c>
-      <c r="C23" s="3">
+        <v>300</v>
+      </c>
+      <c r="C23" s="4">
         <v>0</v>
       </c>
       <c r="D23">
@@ -5146,26 +5269,26 @@
         <v>154</v>
       </c>
       <c r="H23" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="I23" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="J23" t="s">
-        <v>240</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s">
-        <v>293</v>
-      </c>
-      <c r="C24" s="3">
+        <v>303</v>
+      </c>
+      <c r="C24" s="4">
         <v>0</v>
       </c>
       <c r="D24">
@@ -5181,26 +5304,26 @@
         <v>158</v>
       </c>
       <c r="H24" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="I24" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="J24" t="s">
-        <v>224</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
-      </c>
-      <c r="C25" s="3">
+        <v>306</v>
+      </c>
+      <c r="C25" s="4">
         <v>0</v>
       </c>
       <c r="D25">
@@ -5216,24 +5339,24 @@
         <v>151</v>
       </c>
       <c r="H25" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="I25" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="J25" t="s">
-        <v>251</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -5251,21 +5374,21 @@
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I26" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="J26" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B27" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -5283,23 +5406,23 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="I27" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="J27" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B28" t="s">
-        <v>306</v>
-      </c>
-      <c r="C28" s="3">
+        <v>316</v>
+      </c>
+      <c r="C28" s="4">
         <v>0</v>
       </c>
       <c r="D28">
@@ -5315,26 +5438,26 @@
         <v>151</v>
       </c>
       <c r="H28" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="I28" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="J28" t="s">
-        <v>240</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B29" t="s">
-        <v>309</v>
-      </c>
-      <c r="C29" s="3">
+        <v>319</v>
+      </c>
+      <c r="C29" s="4">
         <v>0</v>
       </c>
       <c r="D29">
@@ -5350,26 +5473,26 @@
         <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="I29" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J29" t="s">
-        <v>312</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>225</v>
+        <v>322</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B30" t="s">
-        <v>313</v>
-      </c>
-      <c r="C30" s="3">
+        <v>323</v>
+      </c>
+      <c r="C30" s="4">
         <v>0</v>
       </c>
       <c r="D30">
@@ -5385,26 +5508,26 @@
         <v>149</v>
       </c>
       <c r="H30" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="I30" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="J30" t="s">
-        <v>251</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>225</v>
+        <v>261</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B31" t="s">
-        <v>316</v>
-      </c>
-      <c r="C31" s="3">
+        <v>326</v>
+      </c>
+      <c r="C31" s="4">
         <v>0</v>
       </c>
       <c r="D31">
@@ -5420,24 +5543,24 @@
         <v>148</v>
       </c>
       <c r="H31" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="I31" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="J31" t="s">
-        <v>240</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B32" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -5455,23 +5578,23 @@
         <v>151</v>
       </c>
       <c r="H32" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="I32" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="J32" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B33" t="s">
-        <v>323</v>
-      </c>
-      <c r="C33" s="3">
+        <v>333</v>
+      </c>
+      <c r="C33" s="4">
         <v>0</v>
       </c>
       <c r="D33">
@@ -5487,26 +5610,26 @@
         <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="I33" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="J33" t="s">
-        <v>224</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B34" t="s">
-        <v>327</v>
-      </c>
-      <c r="C34" s="3">
+        <v>337</v>
+      </c>
+      <c r="C34" s="4">
         <v>0</v>
       </c>
       <c r="D34">
@@ -5522,27 +5645,27 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="J34" t="s">
-        <v>329</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>225</v>
+        <v>339</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E35">
         <v>57</v>
@@ -5551,27 +5674,27 @@
         <v>143</v>
       </c>
       <c r="H35" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="I35" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="K35" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E36">
         <v>71</v>
@@ -5580,24 +5703,24 @@
         <v>194</v>
       </c>
       <c r="H36" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="I36" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="J36" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="K36" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B37" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -5615,21 +5738,21 @@
         <v>138</v>
       </c>
       <c r="H37" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="I37" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="J37" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -5647,21 +5770,21 @@
         <v>154</v>
       </c>
       <c r="H38" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="I38" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J38" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -5679,18 +5802,18 @@
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="I39" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -5708,21 +5831,21 @@
         <v>205</v>
       </c>
       <c r="H40" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="I40" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="J40" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -5740,21 +5863,21 @@
         <v>162</v>
       </c>
       <c r="H41" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="I41" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="J41" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -5772,21 +5895,21 @@
         <v>167</v>
       </c>
       <c r="H42" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I42" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="J42" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -5804,21 +5927,21 @@
         <v>170</v>
       </c>
       <c r="H43" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="I43" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="J43" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -5836,21 +5959,21 @@
         <v>164</v>
       </c>
       <c r="H44" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="I44" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="J44" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -5868,18 +5991,18 @@
         <v>141</v>
       </c>
       <c r="H45" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="I45" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B46" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -5897,21 +6020,21 @@
         <v>158</v>
       </c>
       <c r="H46" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="I46" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="J46" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -5929,21 +6052,21 @@
         <v>137</v>
       </c>
       <c r="H47" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="I47" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="J47" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -5961,21 +6084,21 @@
         <v>215</v>
       </c>
       <c r="H48" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="I48" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="J48" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B49" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -5993,21 +6116,21 @@
         <v>182</v>
       </c>
       <c r="H49" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="I49" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="J49" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B50" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6025,21 +6148,21 @@
         <v>158</v>
       </c>
       <c r="H50" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="I50" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="J50" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B51" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6057,21 +6180,21 @@
         <v>73</v>
       </c>
       <c r="H51" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="I51" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="J51" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6089,21 +6212,21 @@
         <v>150</v>
       </c>
       <c r="H52" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="I52" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="J52" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B53" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6121,18 +6244,18 @@
         <v>156</v>
       </c>
       <c r="H53" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="I53" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6150,21 +6273,21 @@
         <v>149</v>
       </c>
       <c r="H54" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="I54" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="J54" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B55" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6182,21 +6305,21 @@
         <v>105</v>
       </c>
       <c r="H55" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="I55" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="J55" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -6214,21 +6337,21 @@
         <v>154</v>
       </c>
       <c r="H56" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="I56" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="J56" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B57" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -6246,21 +6369,21 @@
         <v>328</v>
       </c>
       <c r="H57" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="I57" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="J57" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B58" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -6278,21 +6401,21 @@
         <v>255</v>
       </c>
       <c r="H58" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="I58" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="J58" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B59" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -6310,21 +6433,21 @@
         <v>259</v>
       </c>
       <c r="H59" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="I59" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="J59" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B60" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -6342,21 +6465,21 @@
         <v>281</v>
       </c>
       <c r="H60" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="I60" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="J60" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B61" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -6374,21 +6497,21 @@
         <v>192</v>
       </c>
       <c r="H61" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="I61" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="J61" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B62" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -6406,21 +6529,21 @@
         <v>215</v>
       </c>
       <c r="H62" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="I62" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="J62" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -6438,21 +6561,21 @@
         <v>153</v>
       </c>
       <c r="H63" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="I63" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="J63" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B64" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -6470,21 +6593,21 @@
         <v>182</v>
       </c>
       <c r="H64" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="I64" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="J64" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B65" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6502,21 +6625,21 @@
         <v>199</v>
       </c>
       <c r="H65" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="I65" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="J65" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B66" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6534,21 +6657,21 @@
         <v>182</v>
       </c>
       <c r="H66" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="I66" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="J66" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B67" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -6566,21 +6689,21 @@
         <v>151</v>
       </c>
       <c r="H67" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="I67" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="J67" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B68" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -6598,21 +6721,21 @@
         <v>153</v>
       </c>
       <c r="H68" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="I68" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="J68" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B69" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -6630,21 +6753,21 @@
         <v>155</v>
       </c>
       <c r="H69" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="I69" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="J69" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B70" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6662,21 +6785,21 @@
         <v>148</v>
       </c>
       <c r="H70" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="I70" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="J70" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B71" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6694,21 +6817,21 @@
         <v>193</v>
       </c>
       <c r="H71" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="I71" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="J71" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6726,21 +6849,21 @@
         <v>135</v>
       </c>
       <c r="H72" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="I72" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="J72" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B73" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6758,18 +6881,18 @@
         <v>122</v>
       </c>
       <c r="H73" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="I73" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B74" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6787,21 +6910,21 @@
         <v>180</v>
       </c>
       <c r="H74" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="I74" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="J74" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B75" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6819,21 +6942,21 @@
         <v>148</v>
       </c>
       <c r="H75" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="I75" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="J75" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -6851,21 +6974,21 @@
         <v>154</v>
       </c>
       <c r="H76" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="I76" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="J76" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B77" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -6883,21 +7006,21 @@
         <v>122</v>
       </c>
       <c r="H77" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="I77" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="J77" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B78" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -6915,21 +7038,21 @@
         <v>82</v>
       </c>
       <c r="H78" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="I78" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="J78" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B79" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -6947,27 +7070,27 @@
         <v>89</v>
       </c>
       <c r="H79" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="I79" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="J79" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B80" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E80">
         <v>57</v>
@@ -6976,21 +7099,21 @@
         <v>133</v>
       </c>
       <c r="H80" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="I80" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="K80" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -7008,21 +7131,21 @@
         <v>145</v>
       </c>
       <c r="H81" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="I81" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="J81" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B82" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -7040,18 +7163,18 @@
         <v>146</v>
       </c>
       <c r="H82" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="I82" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7069,21 +7192,21 @@
         <v>81</v>
       </c>
       <c r="H83" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="I83" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="J83" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B84" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7101,18 +7224,18 @@
         <v>142</v>
       </c>
       <c r="H84" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="I84" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B85" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -7130,21 +7253,21 @@
         <v>49</v>
       </c>
       <c r="H85" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="I85" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="J85" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B86" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7162,21 +7285,21 @@
         <v>302</v>
       </c>
       <c r="H86" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="I86" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="J86" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B87" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7194,21 +7317,21 @@
         <v>315</v>
       </c>
       <c r="H87" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="I87" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="J87" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B88" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7226,27 +7349,27 @@
         <v>214</v>
       </c>
       <c r="H88" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="I88" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="J88" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="B89" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E89">
         <v>20</v>
@@ -7255,27 +7378,27 @@
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="J89" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="K89" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="B90" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E90">
         <v>20</v>
@@ -7284,27 +7407,27 @@
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="J90" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="K90" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="B91" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E91">
         <v>21</v>
@@ -7313,27 +7436,27 @@
         <v>0</v>
       </c>
       <c r="H91" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="J91" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="K91" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="B92" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E92">
         <v>24</v>
@@ -7342,17 +7465,17 @@
         <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="J92" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="K92" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K92" xr:uid="{3FEEC501-A461-4B01-A803-6C078EA74428}"/>
+  <autoFilter ref="A1:K92" xr:uid="{662A7064-CBB1-4153-A2CE-0F17B0896B3E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/marketing/auditorias-seo/auditoria-site-consolidada-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/auditoria-site-consolidada-2026-09-25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solveplan-my.sharepoint.com/personal/molina_solveplan_com/Documents/publica equipe/projetos/Pre Venda/Comercial/Marketing/1. MKT Estrategy/3. Agentes de IA/ccos-ratos/marketing/auditorias-seo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\AppData\Local\Temp\claude\c--Users-franc-solveplan-com-Roberto-Molina---Marketing-1--MKT-Estrategy-3--Agentes-de-IA-ccos-ratos\3fe7c38d-8aa5-4234-b9e2-eb8021efc363\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A72556D2-3B1B-4753-A654-C714B075ABD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F0D9676-2676-4674-8CBF-32251BA3D37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0BEFFF4A-346F-4456-8A5C-ED58C33935F1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD7CA5EC-34C0-4562-8467-18DB7D829753}"/>
   </bookViews>
   <sheets>
     <sheet name="Painel" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Varredura 91 URLs" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plano de ação'!$A$1:$J$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Plano de ação'!$A$1:$J$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Varredura 91 URLs'!$A$1:$K$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="573">
   <si>
     <t>Prioridade</t>
   </si>
@@ -150,6 +150,102 @@
     <t>SEO técnico</t>
   </si>
   <si>
+    <t>28 páginas institucionais</t>
+  </si>
+  <si>
+    <t>Adicionar H1</t>
+  </si>
+  <si>
+    <t>Textos aprovados na revisão de 25/09 (revisao-titles-descriptions-h1). Aplicar na volta da Fran, conferindo o visual</t>
+  </si>
+  <si>
+    <t>Elementor &gt; widget Título principal &gt; Tag HTML: H1</t>
+  </si>
+  <si>
+    <t>SEO +7/pág</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Auditoria 28/07 + 25/09</t>
+  </si>
+  <si>
+    <t>Conversão</t>
+  </si>
+  <si>
+    <t>Nova página</t>
+  </si>
+  <si>
+    <t>Landing page BDC para ads</t>
+  </si>
+  <si>
+    <t>LP dedicada para LinkedIn e Google Ads (prioridade H2 2026)</t>
+  </si>
+  <si>
+    <t>Elementor &gt; nova página (noindex se for só para mídia)</t>
+  </si>
+  <si>
+    <t>Pipeline</t>
+  </si>
+  <si>
+    <t>Médio</t>
+  </si>
+  <si>
+    <t>Análise site 25/09 / estratégia H2</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>CTA quebrado</t>
+  </si>
+  <si>
+    <t>"Fale com nossos especialistas" leva para /aceleradores/. Apontar para /contato/ ou para a LP BDC</t>
+  </si>
+  <si>
+    <t>Elementor &gt; botão &gt; Link</t>
+  </si>
+  <si>
+    <t>/contato/</t>
+  </si>
+  <si>
+    <t>Melhorar página de contato</t>
+  </si>
+  <si>
+    <t>Corrigir o horário ("8h-18h e 13h-18h30"), dizer o próximo passo depois do envio, incluir agendamento HubSpot Meetings e H1</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Contato</t>
+  </si>
+  <si>
+    <t>AEO</t>
+  </si>
+  <si>
+    <t>Bloco de snippet</t>
+  </si>
+  <si>
+    <t>H2 "O que a Solveplan faz?" + parágrafo de 54 palavras (texto no relatório site-2026-09-25-analise.md; trocar 390 por 300 projetos)</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Título H2 + Editor de texto</t>
+  </si>
+  <si>
+    <t>Auditoria home 25/09</t>
+  </si>
+  <si>
+    <t>FAQ + FAQPage schema</t>
+  </si>
+  <si>
+    <t>4 perguntas (BDC, Datasphere x BDC, prazo SAC, sair das planilhas) + JSON-LD (código no relatório)</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Acordeão + widget HTML</t>
+  </si>
+  <si>
+    <t>+10 (+7 perguntas nos headings)</t>
+  </si>
+  <si>
     <t>Todas as páginas</t>
   </si>
   <si>
@@ -165,90 +261,120 @@
     <t>GEO +1-2/pág</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
     <t>Auditoria 28/07 + 30/07 + 25/09</t>
   </si>
   <si>
-    <t>28 páginas institucionais</t>
-  </si>
-  <si>
-    <t>Adicionar H1</t>
-  </si>
-  <si>
-    <t>Home, BDC, serviços, contato, sobre e todos os aceleradores estão sem H1. Modelo: /sap-datasphere/</t>
-  </si>
-  <si>
-    <t>Elementor &gt; widget Título principal &gt; Tag HTML: H1</t>
-  </si>
-  <si>
-    <t>SEO +7/pág</t>
-  </si>
-  <si>
-    <t>Auditoria 28/07 + 25/09</t>
-  </si>
-  <si>
-    <t>Conversão</t>
-  </si>
-  <si>
-    <t>/contato/</t>
-  </si>
-  <si>
-    <t>Melhorar página de contato</t>
-  </si>
-  <si>
-    <t>Corrigir o horário ("8h-18h e 13h-18h30"), dizer o próximo passo depois do envio, incluir agendamento HubSpot Meetings e H1</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Contato</t>
-  </si>
-  <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
-    <t>Nova página</t>
-  </si>
-  <si>
-    <t>Landing page BDC para ads</t>
-  </si>
-  <si>
-    <t>LP dedicada para LinkedIn e Google Ads (prioridade H2 2026)</t>
-  </si>
-  <si>
-    <t>Elementor &gt; nova página (noindex se for só para mídia)</t>
-  </si>
-  <si>
-    <t>Médio</t>
-  </si>
-  <si>
-    <t>Análise site 25/09 / estratégia H2</t>
-  </si>
-  <si>
-    <t>AEO</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>FAQ + FAQPage schema</t>
-  </si>
-  <si>
-    <t>4 perguntas (BDC, Datasphere x BDC, prazo SAC, sair das planilhas) + JSON-LD (código no relatório)</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Acordeão + widget HTML</t>
-  </si>
-  <si>
-    <t>+10 (+7 perguntas nos headings)</t>
-  </si>
-  <si>
-    <t>Auditoria home 25/09</t>
-  </si>
-  <si>
     <t>SEO página</t>
   </si>
   <si>
+    <t>H1 com keyword</t>
+  </si>
+  <si>
+    <t>"Consultoria SAP em dados, analytics, planejamento e consolidação"</t>
+  </si>
+  <si>
+    <t>Elementor &gt; título do hero &gt; Tag H1</t>
+  </si>
+  <si>
+    <t>Faixa de prova social</t>
+  </si>
+  <si>
+    <t>Prêmio 2026, prêmio 2025, SAP Gold e logos de clientes logo abaixo do hero</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Home</t>
+  </si>
+  <si>
+    <t>/sap-business-data-cloud/</t>
+  </si>
+  <si>
+    <t>Reescrever página BDC</t>
+  </si>
+  <si>
+    <t>65% do tráfego, 302 palavras genéricas, sem case, sem FAQ, 1 CTA. Estrutura: dor &gt; abordagem Solveplan &gt; case &gt; FAQ &gt; CTA (usar /pagina-solucao)</t>
+  </si>
+  <si>
+    <t>Elementor &gt; página BDC</t>
+  </si>
+  <si>
+    <t>Difícil</t>
+  </si>
+  <si>
+    <t>Contadores legíveis por robôs</t>
+  </si>
+  <si>
+    <t>O HTML entrega "0+" (a animação só roda com JavaScript). Pôr o número real como texto</t>
+  </si>
+  <si>
+    <t>Elementor &gt; widget Contador &gt; valor inicial = valor final, ou widget Título</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>Hero focado em BDC</t>
+  </si>
+  <si>
+    <t>Hero com SAP BDC + selo Melhor Parceiro SAP BDC 2026 LATAM + CTA "Agende um diagnóstico BDC"</t>
+  </si>
+  <si>
+    <t>Elementor &gt; Home &gt; seção hero</t>
+  </si>
+  <si>
+    <t>Post BW/4HANA</t>
+  </si>
+  <si>
+    <t>FAQ com schema</t>
+  </si>
+  <si>
+    <t>A seção FAQ existe, mas falta o schema FAQPage</t>
+  </si>
+  <si>
+    <t>Rank Math Schema Generator ou widget HTML</t>
+  </si>
+  <si>
+    <t>Parcial</t>
+  </si>
+  <si>
+    <t>Auditoria BW/4HANA 17/09</t>
+  </si>
+  <si>
+    <t>/sap-datasphere/</t>
+  </si>
+  <si>
+    <t>A seção "Perguntas frequentes" existe, mas falta o schema FAQPage</t>
+  </si>
+  <si>
+    <t>Widget HTML com JSON-LD FAQPage</t>
+  </si>
+  <si>
+    <t>Auditoria Datasphere 30/07</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>Virou "O que é o SAP Datasphere?"</t>
+  </si>
+  <si>
+    <t>Elementor</t>
+  </si>
+  <si>
+    <t>Headings em pergunta + snippet</t>
+  </si>
+  <si>
+    <t>"Por que o SAP BW não é mais suficiente?", "O que o SAP Datasphere resolve...?"</t>
+  </si>
+  <si>
+    <t>Meta description</t>
+  </si>
+  <si>
+    <t>"Parceira SAP Gold e Melhor Parceiro SAP Business Data Cloud 2026 na América Latina. Analytics, planejamento e consolidação com dados confiáveis." (144)</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Editar snippet &gt; Descrição</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -258,64 +384,40 @@
     <t>Rank Math &gt; Editar snippet &gt; Título</t>
   </si>
   <si>
-    <t>H1 com keyword</t>
-  </si>
-  <si>
-    <t>"Consultoria SAP em dados, analytics, planejamento e consolidação"</t>
-  </si>
-  <si>
-    <t>Elementor &gt; título do hero &gt; Tag H1</t>
-  </si>
-  <si>
-    <t>Bloco de snippet</t>
-  </si>
-  <si>
-    <t>H2 "O que a Solveplan faz?" + parágrafo de 54 palavras (texto no relatório site-2026-09-25-analise.md; trocar 390 por 300 projetos)</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Título H2 + Editor de texto</t>
-  </si>
-  <si>
-    <t>Meta description</t>
-  </si>
-  <si>
-    <t>"Parceira SAP Gold e Melhor Parceiro SAP Business Data Cloud 2026 na América Latina. Analytics, planejamento e consolidação com dados confiáveis." (144)</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Editar snippet &gt; Descrição</t>
-  </si>
-  <si>
-    <t>Hero focado em BDC</t>
-  </si>
-  <si>
-    <t>Hero com SAP BDC + selo Melhor Parceiro SAP BDC 2026 LATAM + CTA "Agende um diagnóstico BDC"</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Home &gt; seção hero</t>
-  </si>
-  <si>
-    <t>/sap-business-data-cloud/</t>
-  </si>
-  <si>
-    <t>Reescrever página BDC</t>
-  </si>
-  <si>
-    <t>65% do tráfego, 302 palavras genéricas, sem case, sem FAQ, 1 CTA. Estrutura: dor &gt; abordagem Solveplan &gt; case &gt; FAQ &gt; CTA (usar /pagina-solucao)</t>
-  </si>
-  <si>
-    <t>Elementor &gt; página BDC</t>
-  </si>
-  <si>
-    <t>Difícil</t>
-  </si>
-  <si>
-    <t>Faixa de prova social</t>
-  </si>
-  <si>
-    <t>Prêmio 2026, prêmio 2025, SAP Gold e logos de clientes logo abaixo do hero</t>
-  </si>
-  <si>
-    <t>Elementor &gt; Home</t>
+    <t>Title e description</t>
+  </si>
+  <si>
+    <t>Title de 60 caracteres e description de 157 aplicados</t>
+  </si>
+  <si>
+    <t>Rank Math</t>
+  </si>
+  <si>
+    <t>Meta description, title e slug</t>
+  </si>
+  <si>
+    <t>Publicado com title de 57 caracteres, description e slug /blog/sap-datasphere-x-sap-bw4hana/</t>
+  </si>
+  <si>
+    <t>Rank Math / permalink</t>
+  </si>
+  <si>
+    <t>/sap-profitability-and-performance-management/</t>
+  </si>
+  <si>
+    <t>PaPM fora do ar</t>
+  </si>
+  <si>
+    <t>Página em rascunho + redirecionamento 301 para /contato/ (Rank Math &gt; Redirecionamentos). Tirar o card de /servicos/ no rascunho dessa página</t>
+  </si>
+  <si>
+    <t>Rank Math / Páginas</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Revisão 25/09</t>
   </si>
   <si>
     <t>Title e description da BDC</t>
@@ -330,66 +432,6 @@
     <t>SEO</t>
   </si>
   <si>
-    <t>Contadores legíveis por robôs</t>
-  </si>
-  <si>
-    <t>O HTML entrega "0+" (a animação só roda com JavaScript). Pôr o número real como texto</t>
-  </si>
-  <si>
-    <t>Elementor &gt; widget Contador &gt; valor inicial = valor final, ou widget Título</t>
-  </si>
-  <si>
-    <t>GEO</t>
-  </si>
-  <si>
-    <t>CTA quebrado</t>
-  </si>
-  <si>
-    <t>"Fale com nossos especialistas" leva para /aceleradores/. Apontar para /contato/ ou para a LP BDC</t>
-  </si>
-  <si>
-    <t>Elementor &gt; botão &gt; Link</t>
-  </si>
-  <si>
-    <t>Post BW/4HANA</t>
-  </si>
-  <si>
-    <t>FAQ com schema</t>
-  </si>
-  <si>
-    <t>A seção FAQ existe, mas falta o schema FAQPage</t>
-  </si>
-  <si>
-    <t>Rank Math Schema Generator ou widget HTML</t>
-  </si>
-  <si>
-    <t>Parcial</t>
-  </si>
-  <si>
-    <t>Auditoria BW/4HANA 17/09</t>
-  </si>
-  <si>
-    <t>/sap-datasphere/</t>
-  </si>
-  <si>
-    <t>A seção "Perguntas frequentes" existe, mas falta o schema FAQPage</t>
-  </si>
-  <si>
-    <t>Widget HTML com JSON-LD FAQPage</t>
-  </si>
-  <si>
-    <t>Auditoria Datasphere 30/07</t>
-  </si>
-  <si>
-    <t>Meta description, title e slug</t>
-  </si>
-  <si>
-    <t>Publicado com title de 57 caracteres, description e slug /blog/sap-datasphere-x-sap-bw4hana/</t>
-  </si>
-  <si>
-    <t>Rank Math / permalink</t>
-  </si>
-  <si>
     <t>Confirmar números oficiais</t>
   </si>
   <si>
@@ -402,33 +444,21 @@
     <t>Credibilidade</t>
   </si>
   <si>
-    <t>Headings em pergunta + snippet</t>
-  </si>
-  <si>
-    <t>"Por que o SAP BW não é mais suficiente?", "O que o SAP Datasphere resolve...?"</t>
-  </si>
-  <si>
-    <t>Elementor</t>
-  </si>
-  <si>
-    <t>Title e description</t>
-  </si>
-  <si>
-    <t>Title de 60 caracteres e description de 157 aplicados</t>
-  </si>
-  <si>
-    <t>Rank Math</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>Virou "O que é o SAP Datasphere?"</t>
-  </si>
-  <si>
     <t>3-Média</t>
   </si>
   <si>
+    <t>Atualizar WordPress 6.8.9 &gt; 7.1.2</t>
+  </si>
+  <si>
+    <t>Salto grande de versão: fazer com backup e testar Elementor antes (idealmente em staging da Hostinger)</t>
+  </si>
+  <si>
+    <t>Painel &gt; Atualizações</t>
+  </si>
+  <si>
+    <t>Sessão 25/09</t>
+  </si>
+  <si>
     <t>Mercado e fonte externa</t>
   </si>
   <si>
@@ -438,6 +468,120 @@
     <t>Elementor &gt; seção Sobre</t>
   </si>
   <si>
+    <t>Blog</t>
+  </si>
+  <si>
+    <t>Canibalização e duplicados</t>
+  </si>
+  <si>
+    <t>governanca-dados-financeiros-sap-bdc x sap-business-data-cloud-governanca-financeira; slugs com "-2". Fundir ou diferenciar + 301</t>
+  </si>
+  <si>
+    <t>Posts + Rank Math &gt; Redirecionamentos</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Home, BDC, Datasphere, BW/4HANA</t>
+  </si>
+  <si>
+    <t>Medir PageSpeed</t>
+  </si>
+  <si>
+    <t>A cota da API estava esgotada em todas as auditorias. Rodar mobile e desktop e registrar LCP/CLS</t>
+  </si>
+  <si>
+    <t>pagespeed.web.dev</t>
+  </si>
+  <si>
+    <t>até +20/pág</t>
+  </si>
+  <si>
+    <t>Todas as auditorias</t>
+  </si>
+  <si>
+    <t>País no schema Organization</t>
+  </si>
+  <si>
+    <t>addressCountry "55" deve ser "BR"</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Títulos e Meta &gt; Local SEO &gt; País</t>
+  </si>
+  <si>
+    <t>Alts de imagens</t>
+  </si>
+  <si>
+    <t>BDC 8/8 sem alt; home 10/31; Datasphere 8/16; BW/4HANA 7/9</t>
+  </si>
+  <si>
+    <t>Mídia &gt; Biblioteca &gt; Texto alternativo</t>
+  </si>
+  <si>
+    <t>SEO +3/pág</t>
+  </si>
+  <si>
+    <t>Auditorias 28/07, 30/07, 17/09, 25/09</t>
+  </si>
+  <si>
+    <t>Sitemap</t>
+  </si>
+  <si>
+    <t>Tirar lixo do índice</t>
+  </si>
+  <si>
+    <t>/banner/banner-2, /banner/banner-3, /video-aceleradores/video-teste/, /midia-em-acelerador/analytics/, /cases-abertos/</t>
+  </si>
+  <si>
+    <t>Aplicado 25/09 por página (noindex). Falta marcar noindex no tipo de post inteiro (Banners, Mídias e Vídeos Aceleradores)</t>
+  </si>
+  <si>
+    <t>Fonte externa (Gartner/IDC)</t>
+  </si>
+  <si>
+    <t>Não confirmado na página atual</t>
+  </si>
+  <si>
+    <t>Elementor &gt; texto de contexto</t>
+  </si>
+  <si>
+    <t>A verificar</t>
+  </si>
+  <si>
+    <t>Prova social e América Latina</t>
+  </si>
+  <si>
+    <t>Gold, prêmio e América Latina já aparecem na página</t>
+  </si>
+  <si>
+    <t>E-E-A-T, América Latina, typos</t>
+  </si>
+  <si>
+    <t>Parágrafo de autoridade, América Latina e correção de "SAP BW/HANA"/"DAP BW" aplicados</t>
+  </si>
+  <si>
+    <t>Corpo do post</t>
+  </si>
+  <si>
+    <t>Blog (41 URLs)</t>
+  </si>
+  <si>
+    <t>Titles acima de 65 caracteres</t>
+  </si>
+  <si>
+    <t>O sufixo " - Solveplan" estoura o limite. Aplicado 25/09 em 39 URLs (2 mantidos por decisão)</t>
+  </si>
+  <si>
+    <t>Contato, Sobre, Analytics, Blog, Serviços</t>
+  </si>
+  <si>
+    <t>Descriptions fracas ou duplicadas</t>
+  </si>
+  <si>
+    <t>"CONTATO", "Sobre Nós", "Analytics", Blog vazia; /servicos/ copia a description da BDC. Reescrever com 120-155 caracteres</t>
+  </si>
+  <si>
     <t>Post Clean Core</t>
   </si>
   <si>
@@ -456,135 +600,6 @@
     <t>SAP BUSINESS DATA CLOUD, FÁBRICA DE BI, CONSOLIDAÇÃO CONTÁBIL etc. Usar caixa normal + keyword</t>
   </si>
   <si>
-    <t>Blog (41 URLs)</t>
-  </si>
-  <si>
-    <t>Titles acima de 65 caracteres</t>
-  </si>
-  <si>
-    <t>O sufixo " - Solveplan" estoura o limite. Tirar o sufixo nos posts ou encurtar</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Títulos e Meta &gt; Posts &gt; Título</t>
-  </si>
-  <si>
-    <t>País no schema Organization</t>
-  </si>
-  <si>
-    <t>addressCountry "55" deve ser "BR"</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Títulos e Meta &gt; Local SEO &gt; País</t>
-  </si>
-  <si>
-    <t>Sitemap</t>
-  </si>
-  <si>
-    <t>Tirar lixo do índice</t>
-  </si>
-  <si>
-    <t>/banner/banner-2, /banner/banner-3, /video-aceleradores/video-teste/, /midia-em-acelerador/analytics/, /cases-abertos/</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Títulos e Meta &gt; cada tipo de post &gt; noindex e remover do sitemap</t>
-  </si>
-  <si>
-    <t>Atualizar WordPress 6.8.9 &gt; 7.1.2</t>
-  </si>
-  <si>
-    <t>Salto grande de versão: fazer com backup e testar Elementor antes (idealmente em staging da Hostinger)</t>
-  </si>
-  <si>
-    <t>Painel &gt; Atualizações</t>
-  </si>
-  <si>
-    <t>Sessão 25/09</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Home, BDC, Datasphere, BW/4HANA</t>
-  </si>
-  <si>
-    <t>Medir PageSpeed</t>
-  </si>
-  <si>
-    <t>A cota da API estava esgotada em todas as auditorias. Rodar mobile e desktop e registrar LCP/CLS</t>
-  </si>
-  <si>
-    <t>pagespeed.web.dev</t>
-  </si>
-  <si>
-    <t>até +20/pág</t>
-  </si>
-  <si>
-    <t>Todas as auditorias</t>
-  </si>
-  <si>
-    <t>Contato, Sobre, Analytics, Blog, Serviços</t>
-  </si>
-  <si>
-    <t>Descriptions fracas ou duplicadas</t>
-  </si>
-  <si>
-    <t>"CONTATO", "Sobre Nós", "Analytics", Blog vazia; /servicos/ copia a description da BDC. Reescrever com 120-155 caracteres</t>
-  </si>
-  <si>
-    <t>Blog</t>
-  </si>
-  <si>
-    <t>Canibalização e duplicados</t>
-  </si>
-  <si>
-    <t>governanca-dados-financeiros-sap-bdc x sap-business-data-cloud-governanca-financeira; slugs com "-2". Fundir ou diferenciar + 301</t>
-  </si>
-  <si>
-    <t>Posts + Rank Math &gt; Redirecionamentos</t>
-  </si>
-  <si>
-    <t>Alts de imagens</t>
-  </si>
-  <si>
-    <t>BDC 8/8 sem alt; home 10/31; Datasphere 8/16; BW/4HANA 7/9</t>
-  </si>
-  <si>
-    <t>Mídia &gt; Biblioteca &gt; Texto alternativo</t>
-  </si>
-  <si>
-    <t>SEO +3/pág</t>
-  </si>
-  <si>
-    <t>Auditorias 28/07, 30/07, 17/09, 25/09</t>
-  </si>
-  <si>
-    <t>Fonte externa (Gartner/IDC)</t>
-  </si>
-  <si>
-    <t>Não confirmado na página atual</t>
-  </si>
-  <si>
-    <t>Elementor &gt; texto de contexto</t>
-  </si>
-  <si>
-    <t>A verificar</t>
-  </si>
-  <si>
-    <t>Prova social e América Latina</t>
-  </si>
-  <si>
-    <t>Gold, prêmio e América Latina já aparecem na página</t>
-  </si>
-  <si>
-    <t>E-E-A-T, América Latina, typos</t>
-  </si>
-  <si>
-    <t>Parágrafo de autoridade, América Latina e correção de "SAP BW/HANA"/"DAP BW" aplicados</t>
-  </si>
-  <si>
-    <t>Corpo do post</t>
-  </si>
-  <si>
     <t>4-Baixa</t>
   </si>
   <si>
@@ -615,6 +630,18 @@
     <t>Image Optimization &gt; Configurações &gt; WebP</t>
   </si>
   <si>
+    <t>og:image</t>
+  </si>
+  <si>
+    <t>561x374 e alt "Home". Trocar por 1200x630 com marca + selo do prêmio</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Títulos e Meta &gt; Global &gt; OpenGraph</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
     <t>Conteúdo</t>
   </si>
   <si>
@@ -627,18 +654,6 @@
     <t>Aparência &gt; Menus / Elementor rodapé / notícias</t>
   </si>
   <si>
-    <t>og:image</t>
-  </si>
-  <si>
-    <t>561x374 e alt "Home". Trocar por 1200x630 com marca + selo do prêmio</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Títulos e Meta &gt; Global &gt; OpenGraph</t>
-  </si>
-  <si>
-    <t>Social</t>
-  </si>
-  <si>
     <t>Links internos no corpo</t>
   </si>
   <si>
@@ -1614,7 +1629,7 @@
     <t>Auditoria consolidada — solveplan.com</t>
   </si>
   <si>
-    <t>Consolida as auditorias de 28/07 (site), 30/07 (Datasphere), 17/09 (BW/4HANA) e 25/09 (home + varredura de 91 URLs). Atualizado em 25/09/2026 (segurança concluída).</t>
+    <t>Consolida as auditorias de 28/07 (site), 30/07 (Datasphere), 17/09 (BW/4HANA) e 25/09 (home + varredura de 91 URLs). Atualizado em 25/09/2026 (segurança + 72 titles/descriptions/noindex aplicados).</t>
   </si>
   <si>
     <t>Diagnóstico em uma frase</t>
@@ -2252,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E0B5BF-A688-4A60-9E65-75974B332389}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A236C6D-D2B5-452C-8C3C-F12A92A083D4}">
   <dimension ref="B1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2264,7 +2279,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B1" s="22" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -2272,7 +2287,7 @@
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="23" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -2280,7 +2295,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="24" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -2288,7 +2303,7 @@
     </row>
     <row r="5" spans="2:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="15" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -2296,21 +2311,21 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C8" s="25">
         <v>30</v>
@@ -2319,12 +2334,12 @@
         <v>28</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C9" s="25">
         <v>84</v>
@@ -2333,71 +2348,71 @@
         <v>91</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="D10" s="25">
         <v>26</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="C11" s="25">
         <v>30</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -2407,20 +2422,20 @@
         <v>39</v>
       </c>
       <c r="C16" s="17">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C17" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -2431,104 +2446,104 @@
         <v>18</v>
       </c>
       <c r="C19" s="17">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C20" s="26">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C23" s="15" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="7" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="7" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="7" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="7" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="7" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="7" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="15" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
@@ -2553,8 +2568,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65ABC09B-8826-4137-BD33-1F4E1F877729}">
-  <dimension ref="A1:J48"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF1BF60-CF2F-4222-A046-DC50B3BFA3CF}">
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -2797,31 +2812,31 @@
         <v>32</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2829,22 +2844,22 @@
         <v>32</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>17</v>
@@ -2861,7 +2876,7 @@
         <v>32</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>53</v>
@@ -2876,103 +2891,103 @@
         <v>56</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>64</v>
+      <c r="G11" s="9">
+        <v>10</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="9">
-        <v>8</v>
+        <v>64</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="D13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="9">
-        <v>7</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>17</v>
@@ -2981,18 +2996,18 @@
         <v>39</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>73</v>
@@ -3004,7 +3019,7 @@
         <v>75</v>
       </c>
       <c r="G14" s="9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>17</v>
@@ -3013,18 +3028,18 @@
         <v>39</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>76</v>
@@ -3035,8 +3050,8 @@
       <c r="F15" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G15" s="9">
-        <v>3</v>
+      <c r="G15" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>17</v>
@@ -3045,7 +3060,7 @@
         <v>39</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3053,25 +3068,25 @@
         <v>32</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>39</v>
@@ -3085,25 +3100,25 @@
         <v>32</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>39</v>
@@ -3112,30 +3127,30 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>17</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>39</v>
@@ -3144,100 +3159,100 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="9">
+        <v>2</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>39</v>
+      <c r="I19" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="9">
+        <v>2</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="9" t="s">
+      <c r="I20" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>39</v>
-      </c>
       <c r="J20" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>52</v>
+        <v>103</v>
+      </c>
+      <c r="G21" s="9">
+        <v>7</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="11" t="s">
-        <v>39</v>
+      <c r="I21" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -3245,86 +3260,86 @@
         <v>32</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E22" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>104</v>
-      </c>
       <c r="G22" s="9">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>105</v>
+        <v>17</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E23" s="9" t="s">
+      <c r="F23" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>109</v>
-      </c>
       <c r="G23" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>105</v>
+        <v>17</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="D24" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>113</v>
-      </c>
       <c r="G24" s="9">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>17</v>
@@ -3333,30 +3348,30 @@
         <v>18</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>117</v>
+      <c r="G25" s="9">
+        <v>4</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>17</v>
@@ -3365,30 +3380,30 @@
         <v>18</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G26" s="9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>17</v>
@@ -3397,30 +3412,30 @@
         <v>18</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="G27" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="9">
-        <v>4</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>17</v>
@@ -3429,18 +3444,18 @@
         <v>18</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>124</v>
@@ -3449,10 +3464,10 @@
         <v>125</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G28" s="9">
-        <v>7</v>
+        <v>126</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>17</v>
@@ -3461,94 +3476,94 @@
         <v>18</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G29" s="9">
-        <v>2</v>
+        <v>130</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>131</v>
       </c>
       <c r="H29" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="11" t="s">
-        <v>39</v>
+      <c r="I29" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>93</v>
+        <v>139</v>
+      </c>
+      <c r="G31" s="9">
+        <v>2</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>17</v>
@@ -3557,33 +3572,33 @@
         <v>39</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>39</v>
@@ -3592,27 +3607,27 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>97</v>
+        <v>149</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>17</v>
@@ -3621,30 +3636,30 @@
         <v>39</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>17</v>
@@ -3658,217 +3673,217 @@
     </row>
     <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="11" t="s">
-        <v>39</v>
+      <c r="I36" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>93</v>
+        <v>165</v>
+      </c>
+      <c r="G37" s="9">
+        <v>1</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="11" t="s">
-        <v>39</v>
+      <c r="I37" s="13" t="s">
+        <v>166</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G38" s="9" t="s">
-        <v>93</v>
+        <v>103</v>
+      </c>
+      <c r="G38" s="9">
+        <v>3</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>39</v>
+        <v>17</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>168</v>
+        <v>171</v>
+      </c>
+      <c r="G39" s="9">
+        <v>6</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>39</v>
+      <c r="I39" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B40" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="G40" s="9">
-        <v>1</v>
+      <c r="G40" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="13" t="s">
-        <v>173</v>
+      <c r="I40" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B41" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G41" s="9">
-        <v>3</v>
+      <c r="G41" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>17</v>
@@ -3877,30 +3892,30 @@
         <v>18</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F42" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G42" s="9">
-        <v>6</v>
+      <c r="G42" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>17</v>
@@ -3909,62 +3924,62 @@
         <v>18</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>106</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>12</v>
+        <v>181</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>16</v>
+        <v>127</v>
       </c>
       <c r="H43" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I43" s="11" t="s">
-        <v>39</v>
+      <c r="I43" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G44" s="9">
-        <v>1</v>
+        <v>187</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>16</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>17</v>
@@ -3973,30 +3988,30 @@
         <v>39</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>151</v>
+        <v>190</v>
+      </c>
+      <c r="G45" s="9">
+        <v>1</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>17</v>
@@ -4005,30 +4020,30 @@
         <v>39</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="H46" s="9" t="s">
         <v>17</v>
@@ -4042,7 +4057,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>33</v>
@@ -4051,16 +4066,16 @@
         <v>12</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H47" s="9" t="s">
         <v>17</v>
@@ -4074,44 +4089,76 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="G48" s="9">
-        <v>1</v>
+        <v>201</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>131</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I48" s="13" t="s">
-        <v>173</v>
+      <c r="I48" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>110</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" s="9">
+        <v>1</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J48" xr:uid="{65ABC09B-8826-4137-BD33-1F4E1F877729}"/>
+  <autoFilter ref="A1:J49" xr:uid="{FBF1BF60-CF2F-4222-A046-DC50B3BFA3CF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C942FDC-0ABF-4656-9439-8CB43AD7A5A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC969702-A1B1-42F2-A3CF-74794DB0AC20}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4124,30 +4171,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C2" s="17">
         <v>10</v>
@@ -4164,10 +4211,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C3" s="17">
         <v>10</v>
@@ -4184,10 +4231,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C4" s="17">
         <v>10</v>
@@ -4204,10 +4251,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C5" s="17">
         <v>10</v>
@@ -4224,10 +4271,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C6" s="17">
         <v>8</v>
@@ -4244,10 +4291,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C7" s="17">
         <v>5</v>
@@ -4264,10 +4311,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C8" s="17">
         <v>4</v>
@@ -4284,10 +4331,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B9" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C9" s="17">
         <v>3</v>
@@ -4304,10 +4351,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C10" s="17">
         <v>10</v>
@@ -4324,10 +4371,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C11" s="17">
         <v>8</v>
@@ -4344,10 +4391,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C12" s="17">
         <v>7</v>
@@ -4364,10 +4411,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C13" s="17">
         <v>6</v>
@@ -4384,10 +4431,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C14" s="17">
         <v>5</v>
@@ -4404,10 +4451,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C15" s="17">
         <v>4</v>
@@ -4424,7 +4471,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="21">
@@ -4446,7 +4493,7 @@
     </row>
     <row r="18" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -4463,7 +4510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662A7064-CBB1-4153-A2CE-0F17B0896B3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995648DB-74D7-43ED-80E9-BBF3C5110EBC}">
   <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4481,45 +4528,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C2" s="4">
         <v>0</v>
@@ -4537,24 +4584,24 @@
         <v>44</v>
       </c>
       <c r="H2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="J2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -4572,21 +4619,21 @@
         <v>156</v>
       </c>
       <c r="H3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C4" s="4">
         <v>0</v>
@@ -4604,24 +4651,24 @@
         <v>188</v>
       </c>
       <c r="H4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="J4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
@@ -4639,24 +4686,24 @@
         <v>158</v>
       </c>
       <c r="H5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I5" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J5" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
@@ -4674,24 +4721,24 @@
         <v>156</v>
       </c>
       <c r="H6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="J6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B7" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C7" s="4">
         <v>0</v>
@@ -4709,24 +4756,24 @@
         <v>98</v>
       </c>
       <c r="H7" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I7" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="J7" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C8" s="4">
         <v>0</v>
@@ -4744,24 +4791,24 @@
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I8" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="J8" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C9" s="4">
         <v>0</v>
@@ -4779,24 +4826,24 @@
         <v>155</v>
       </c>
       <c r="H9" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I9" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="J9" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C10" s="4">
         <v>0</v>
@@ -4814,24 +4861,24 @@
         <v>147</v>
       </c>
       <c r="H10" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I10" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="J10" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B11" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C11" s="4">
         <v>0</v>
@@ -4849,24 +4896,24 @@
         <v>155</v>
       </c>
       <c r="H11" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I11" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="J11" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C12" s="4">
         <v>0</v>
@@ -4884,24 +4931,24 @@
         <v>158</v>
       </c>
       <c r="H12" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I12" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B13" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C13" s="4">
         <v>0</v>
@@ -4919,24 +4966,24 @@
         <v>9</v>
       </c>
       <c r="H13" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="I13" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="J13" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B14" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C14" s="4">
         <v>0</v>
@@ -4954,24 +5001,24 @@
         <v>154</v>
       </c>
       <c r="H14" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="I14" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B15" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C15" s="4">
         <v>0</v>
@@ -4989,24 +5036,24 @@
         <v>154</v>
       </c>
       <c r="H15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I15" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="J15" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B16" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C16" s="4">
         <v>0</v>
@@ -5024,24 +5071,24 @@
         <v>9</v>
       </c>
       <c r="H16" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="I16" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J16" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C17" s="4">
         <v>0</v>
@@ -5059,24 +5106,24 @@
         <v>156</v>
       </c>
       <c r="H17" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I17" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="J17" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B18" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C18" s="4">
         <v>0</v>
@@ -5094,24 +5141,24 @@
         <v>157</v>
       </c>
       <c r="H18" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="I18" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J18" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B19" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C19" s="4">
         <v>0</v>
@@ -5129,24 +5176,24 @@
         <v>156</v>
       </c>
       <c r="H19" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I19" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="J19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C20" s="4">
         <v>0</v>
@@ -5164,24 +5211,24 @@
         <v>157</v>
       </c>
       <c r="H20" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J20" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C21" s="4">
         <v>0</v>
@@ -5199,24 +5246,24 @@
         <v>154</v>
       </c>
       <c r="H21" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="I21" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="J21" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C22" s="4">
         <v>0</v>
@@ -5234,24 +5281,24 @@
         <v>156</v>
       </c>
       <c r="H22" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="I22" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J22" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C23" s="4">
         <v>0</v>
@@ -5269,24 +5316,24 @@
         <v>154</v>
       </c>
       <c r="H23" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I23" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J23" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C24" s="4">
         <v>0</v>
@@ -5304,24 +5351,24 @@
         <v>158</v>
       </c>
       <c r="H24" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="I24" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J24" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C25" s="4">
         <v>0</v>
@@ -5339,24 +5386,24 @@
         <v>151</v>
       </c>
       <c r="H25" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="I25" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="J25" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -5374,21 +5421,21 @@
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="I26" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J26" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -5406,21 +5453,21 @@
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="I27" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J27" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C28" s="4">
         <v>0</v>
@@ -5438,24 +5485,24 @@
         <v>151</v>
       </c>
       <c r="H28" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I28" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J28" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C29" s="4">
         <v>0</v>
@@ -5473,24 +5520,24 @@
         <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I29" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J29" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B30" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C30" s="4">
         <v>0</v>
@@ -5508,24 +5555,24 @@
         <v>149</v>
       </c>
       <c r="H30" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="I30" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J30" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C31" s="4">
         <v>0</v>
@@ -5543,24 +5590,24 @@
         <v>148</v>
       </c>
       <c r="H31" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="I31" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J31" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B32" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -5578,21 +5625,21 @@
         <v>151</v>
       </c>
       <c r="H32" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I32" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J32" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B33" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C33" s="4">
         <v>0</v>
@@ -5610,24 +5657,24 @@
         <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="I33" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J33" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B34" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>
@@ -5645,27 +5692,27 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J34" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E35">
         <v>57</v>
@@ -5674,27 +5721,27 @@
         <v>143</v>
       </c>
       <c r="H35" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I35" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="K35" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E36">
         <v>71</v>
@@ -5703,24 +5750,24 @@
         <v>194</v>
       </c>
       <c r="H36" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="I36" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J36" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K36" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -5738,21 +5785,21 @@
         <v>138</v>
       </c>
       <c r="H37" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="I37" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J37" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B38" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -5770,21 +5817,21 @@
         <v>154</v>
       </c>
       <c r="H38" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="I38" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J38" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -5802,18 +5849,18 @@
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="I39" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -5831,21 +5878,21 @@
         <v>205</v>
       </c>
       <c r="H40" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="I40" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J40" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -5863,21 +5910,21 @@
         <v>162</v>
       </c>
       <c r="H41" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="I41" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="J41" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -5895,21 +5942,21 @@
         <v>167</v>
       </c>
       <c r="H42" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I42" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J42" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -5927,21 +5974,21 @@
         <v>170</v>
       </c>
       <c r="H43" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="I43" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J43" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -5959,21 +6006,21 @@
         <v>164</v>
       </c>
       <c r="H44" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="I44" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="J44" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -5991,18 +6038,18 @@
         <v>141</v>
       </c>
       <c r="H45" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="I45" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -6020,21 +6067,21 @@
         <v>158</v>
       </c>
       <c r="H46" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="I46" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J46" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6052,21 +6099,21 @@
         <v>137</v>
       </c>
       <c r="H47" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I47" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J47" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -6084,21 +6131,21 @@
         <v>215</v>
       </c>
       <c r="H48" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="I48" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J48" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -6116,21 +6163,21 @@
         <v>182</v>
       </c>
       <c r="H49" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="I49" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J49" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -6148,21 +6195,21 @@
         <v>158</v>
       </c>
       <c r="H50" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="I50" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J50" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B51" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -6180,21 +6227,21 @@
         <v>73</v>
       </c>
       <c r="H51" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="I51" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J51" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B52" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -6212,21 +6259,21 @@
         <v>150</v>
       </c>
       <c r="H52" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="I52" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J52" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -6244,18 +6291,18 @@
         <v>156</v>
       </c>
       <c r="H53" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="I53" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -6273,21 +6320,21 @@
         <v>149</v>
       </c>
       <c r="H54" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="I54" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J54" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -6305,21 +6352,21 @@
         <v>105</v>
       </c>
       <c r="H55" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="I55" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J55" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B56" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -6337,21 +6384,21 @@
         <v>154</v>
       </c>
       <c r="H56" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="I56" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J56" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B57" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -6369,21 +6416,21 @@
         <v>328</v>
       </c>
       <c r="H57" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="I57" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J57" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -6401,21 +6448,21 @@
         <v>255</v>
       </c>
       <c r="H58" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="I58" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J58" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B59" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -6433,21 +6480,21 @@
         <v>259</v>
       </c>
       <c r="H59" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="I59" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J59" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -6465,21 +6512,21 @@
         <v>281</v>
       </c>
       <c r="H60" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="I60" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J60" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B61" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -6497,21 +6544,21 @@
         <v>192</v>
       </c>
       <c r="H61" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="I61" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J61" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B62" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -6529,21 +6576,21 @@
         <v>215</v>
       </c>
       <c r="H62" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="I62" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="J62" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B63" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -6561,21 +6608,21 @@
         <v>153</v>
       </c>
       <c r="H63" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="I63" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="J63" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -6593,21 +6640,21 @@
         <v>182</v>
       </c>
       <c r="H64" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="I64" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="J64" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B65" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6625,21 +6672,21 @@
         <v>199</v>
       </c>
       <c r="H65" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="I65" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J65" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B66" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6657,21 +6704,21 @@
         <v>182</v>
       </c>
       <c r="H66" t="s">
+        <v>444</v>
+      </c>
+      <c r="I66" t="s">
         <v>439</v>
       </c>
-      <c r="I66" t="s">
-        <v>434</v>
-      </c>
       <c r="J66" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B67" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -6689,21 +6736,21 @@
         <v>151</v>
       </c>
       <c r="H67" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="I67" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="J67" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B68" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -6721,21 +6768,21 @@
         <v>153</v>
       </c>
       <c r="H68" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="I68" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="J68" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B69" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -6753,21 +6800,21 @@
         <v>155</v>
       </c>
       <c r="H69" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="I69" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="J69" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B70" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6785,21 +6832,21 @@
         <v>148</v>
       </c>
       <c r="H70" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="I70" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="J70" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B71" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6817,21 +6864,21 @@
         <v>193</v>
       </c>
       <c r="H71" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="I71" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="J71" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B72" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6849,21 +6896,21 @@
         <v>135</v>
       </c>
       <c r="H72" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="I72" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J72" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B73" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6881,18 +6928,18 @@
         <v>122</v>
       </c>
       <c r="H73" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="I73" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B74" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6910,21 +6957,21 @@
         <v>180</v>
       </c>
       <c r="H74" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="I74" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="J74" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B75" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6942,21 +6989,21 @@
         <v>148</v>
       </c>
       <c r="H75" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="I75" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="J75" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -6974,21 +7021,21 @@
         <v>154</v>
       </c>
       <c r="H76" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="I76" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="J76" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B77" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -7006,21 +7053,21 @@
         <v>122</v>
       </c>
       <c r="H77" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="I77" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="J77" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -7038,21 +7085,21 @@
         <v>82</v>
       </c>
       <c r="H78" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I78" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="J78" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B79" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -7070,27 +7117,27 @@
         <v>89</v>
       </c>
       <c r="H79" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="I79" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="J79" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B80" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E80">
         <v>57</v>
@@ -7099,21 +7146,21 @@
         <v>133</v>
       </c>
       <c r="H80" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="I80" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K80" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B81" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -7131,21 +7178,21 @@
         <v>145</v>
       </c>
       <c r="H81" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="I81" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="J81" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B82" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -7163,18 +7210,18 @@
         <v>146</v>
       </c>
       <c r="H82" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="I82" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -7192,21 +7239,21 @@
         <v>81</v>
       </c>
       <c r="H83" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="I83" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="J83" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -7224,18 +7271,18 @@
         <v>142</v>
       </c>
       <c r="H84" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="I84" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B85" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -7253,21 +7300,21 @@
         <v>49</v>
       </c>
       <c r="H85" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="I85" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="J85" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B86" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -7285,21 +7332,21 @@
         <v>302</v>
       </c>
       <c r="H86" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="I86" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="J86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B87" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -7317,21 +7364,21 @@
         <v>315</v>
       </c>
       <c r="H87" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="I87" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="J87" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B88" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7349,27 +7396,27 @@
         <v>214</v>
       </c>
       <c r="H88" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="I88" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="J88" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B89" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E89">
         <v>20</v>
@@ -7378,27 +7425,27 @@
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="J89" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K89" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B90" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E90">
         <v>20</v>
@@ -7407,27 +7454,27 @@
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="J90" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K90" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B91" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E91">
         <v>21</v>
@@ -7436,27 +7483,27 @@
         <v>0</v>
       </c>
       <c r="H91" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="J91" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K91" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B92" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E92">
         <v>24</v>
@@ -7465,17 +7512,17 @@
         <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="J92" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K92" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K92" xr:uid="{662A7064-CBB1-4153-A2CE-0F17B0896B3E}"/>
+  <autoFilter ref="A1:K92" xr:uid="{995648DB-74D7-43ED-80E9-BBF3C5110EBC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/marketing/auditorias-seo/auditoria-site-consolidada-2026-09-25.xlsx
+++ b/marketing/auditorias-seo/auditoria-site-consolidada-2026-09-25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\AppData\Local\Temp\claude\c--Users-franc-solveplan-com-Roberto-Molina---Marketing-1--MKT-Estrategy-3--Agentes-de-IA-ccos-ratos\3fe7c38d-8aa5-4234-b9e2-eb8021efc363\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F0D9676-2676-4674-8CBF-32251BA3D37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5525B410-07F9-440B-A988-FFAC0A6AD8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD7CA5EC-34C0-4562-8467-18DB7D829753}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CDF2F262-10F8-4AC9-A901-987D36AEC4B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Painel" sheetId="1" r:id="rId1"/>
@@ -321,34 +321,70 @@
     <t>Elementor &gt; Home &gt; seção hero</t>
   </si>
   <si>
+    <t>/sap-datasphere/</t>
+  </si>
+  <si>
+    <t>FAQ com schema</t>
+  </si>
+  <si>
+    <t>A seção "Perguntas frequentes" existe, mas falta o schema FAQPage</t>
+  </si>
+  <si>
+    <t>Widget HTML com JSON-LD FAQPage</t>
+  </si>
+  <si>
+    <t>Parcial</t>
+  </si>
+  <si>
+    <t>Auditoria Datasphere 30/07</t>
+  </si>
+  <si>
     <t>Post BW/4HANA</t>
   </si>
   <si>
-    <t>FAQ com schema</t>
-  </si>
-  <si>
     <t>A seção FAQ existe, mas falta o schema FAQPage</t>
   </si>
   <si>
     <t>Rank Math Schema Generator ou widget HTML</t>
   </si>
   <si>
-    <t>Parcial</t>
-  </si>
-  <si>
     <t>Auditoria BW/4HANA 17/09</t>
   </si>
   <si>
-    <t>/sap-datasphere/</t>
-  </si>
-  <si>
-    <t>A seção "Perguntas frequentes" existe, mas falta o schema FAQPage</t>
-  </si>
-  <si>
-    <t>Widget HTML com JSON-LD FAQPage</t>
-  </si>
-  <si>
-    <t>Auditoria Datasphere 30/07</t>
+    <t>Headings em pergunta + snippet</t>
+  </si>
+  <si>
+    <t>"Por que o SAP BW não é mais suficiente?", "O que o SAP Datasphere resolve...?"</t>
+  </si>
+  <si>
+    <t>Elementor</t>
+  </si>
+  <si>
+    <t>Title e description</t>
+  </si>
+  <si>
+    <t>Title de 60 caracteres e description de 157 aplicados</t>
+  </si>
+  <si>
+    <t>Rank Math</t>
+  </si>
+  <si>
+    <t>Meta description</t>
+  </si>
+  <si>
+    <t>"Parceira SAP Gold e Melhor Parceiro SAP Business Data Cloud 2026 na América Latina. Analytics, planejamento e consolidação com dados confiáveis." (144)</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Editar snippet &gt; Descrição</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>"Consultoria SAP BDC, Analytics e Planejamento | Solveplan" (57 caracteres)</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Editar snippet &gt; Título</t>
   </si>
   <si>
     <t>H1</t>
@@ -357,40 +393,22 @@
     <t>Virou "O que é o SAP Datasphere?"</t>
   </si>
   <si>
-    <t>Elementor</t>
-  </si>
-  <si>
-    <t>Headings em pergunta + snippet</t>
-  </si>
-  <si>
-    <t>"Por que o SAP BW não é mais suficiente?", "O que o SAP Datasphere resolve...?"</t>
-  </si>
-  <si>
-    <t>Meta description</t>
-  </si>
-  <si>
-    <t>"Parceira SAP Gold e Melhor Parceiro SAP Business Data Cloud 2026 na América Latina. Analytics, planejamento e consolidação com dados confiáveis." (144)</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Editar snippet &gt; Descrição</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>"Consultoria SAP BDC, Analytics e Planejamento | Solveplan" (57 caracteres)</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Editar snippet &gt; Título</t>
-  </si>
-  <si>
-    <t>Title e description</t>
-  </si>
-  <si>
-    <t>Title de 60 caracteres e description de 157 aplicados</t>
-  </si>
-  <si>
-    <t>Rank Math</t>
+    <t>/sap-profitability-and-performance-management/</t>
+  </si>
+  <si>
+    <t>PaPM fora do ar</t>
+  </si>
+  <si>
+    <t>Página em rascunho + redirecionamento 301 para /contato/ (Rank Math &gt; Redirecionamentos). Tirar o card de /servicos/ no rascunho dessa página</t>
+  </si>
+  <si>
+    <t>Rank Math / Páginas</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Revisão 25/09</t>
   </si>
   <si>
     <t>Meta description, title e slug</t>
@@ -402,22 +420,16 @@
     <t>Rank Math / permalink</t>
   </si>
   <si>
-    <t>/sap-profitability-and-performance-management/</t>
-  </si>
-  <si>
-    <t>PaPM fora do ar</t>
-  </si>
-  <si>
-    <t>Página em rascunho + redirecionamento 301 para /contato/ (Rank Math &gt; Redirecionamentos). Tirar o card de /servicos/ no rascunho dessa página</t>
-  </si>
-  <si>
-    <t>Rank Math / Páginas</t>
-  </si>
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>Revisão 25/09</t>
+    <t>Confirmar números oficiais</t>
+  </si>
+  <si>
+    <t>Site: 150+ empresas / 300+ projetos / 68+ especialistas. Contexto interno: 150+ / 390+ / 60+. Definir o oficial e atualizar</t>
+  </si>
+  <si>
+    <t>Definido em 25/09: oficiais são os do site (150+ / 300+ / 68+ / 13+). Manter contadores</t>
+  </si>
+  <si>
+    <t>Credibilidade</t>
   </si>
   <si>
     <t>Title e description da BDC</t>
@@ -432,18 +444,6 @@
     <t>SEO</t>
   </si>
   <si>
-    <t>Confirmar números oficiais</t>
-  </si>
-  <si>
-    <t>Site: 150+ empresas / 300+ projetos / 68+ especialistas. Contexto interno: 150+ / 390+ / 60+. Definir o oficial e atualizar</t>
-  </si>
-  <si>
-    <t>Definido em 25/09: oficiais são os do site (150+ / 300+ / 68+ / 13+). Manter contadores</t>
-  </si>
-  <si>
-    <t>Credibilidade</t>
-  </si>
-  <si>
     <t>3-Média</t>
   </si>
   <si>
@@ -468,6 +468,15 @@
     <t>Elementor &gt; seção Sobre</t>
   </si>
   <si>
+    <t>País no schema Organization</t>
+  </si>
+  <si>
+    <t>addressCountry "55" deve ser "BR"</t>
+  </si>
+  <si>
+    <t>Rank Math &gt; Títulos e Meta &gt; Local SEO &gt; País</t>
+  </si>
+  <si>
     <t>Blog</t>
   </si>
   <si>
@@ -480,6 +489,21 @@
     <t>Posts + Rank Math &gt; Redirecionamentos</t>
   </si>
   <si>
+    <t>Alts de imagens</t>
+  </si>
+  <si>
+    <t>BDC 8/8 sem alt; home 10/31; Datasphere 8/16; BW/4HANA 7/9</t>
+  </si>
+  <si>
+    <t>Mídia &gt; Biblioteca &gt; Texto alternativo</t>
+  </si>
+  <si>
+    <t>SEO +3/pág</t>
+  </si>
+  <si>
+    <t>Auditorias 28/07, 30/07, 17/09, 25/09</t>
+  </si>
+  <si>
     <t>Performance</t>
   </si>
   <si>
@@ -501,28 +525,40 @@
     <t>Todas as auditorias</t>
   </si>
   <si>
-    <t>País no schema Organization</t>
-  </si>
-  <si>
-    <t>addressCountry "55" deve ser "BR"</t>
-  </si>
-  <si>
-    <t>Rank Math &gt; Títulos e Meta &gt; Local SEO &gt; País</t>
-  </si>
-  <si>
-    <t>Alts de imagens</t>
-  </si>
-  <si>
-    <t>BDC 8/8 sem alt; home 10/31; Datasphere 8/16; BW/4HANA 7/9</t>
-  </si>
-  <si>
-    <t>Mídia &gt; Biblioteca &gt; Texto alternativo</t>
-  </si>
-  <si>
-    <t>SEO +3/pág</t>
-  </si>
-  <si>
-    <t>Auditorias 28/07, 30/07, 17/09, 25/09</t>
+    <t>Fonte externa (Gartner/IDC)</t>
+  </si>
+  <si>
+    <t>Não confirmado na página atual</t>
+  </si>
+  <si>
+    <t>Elementor &gt; texto de contexto</t>
+  </si>
+  <si>
+    <t>A verificar</t>
+  </si>
+  <si>
+    <t>Prova social e América Latina</t>
+  </si>
+  <si>
+    <t>Gold, prêmio e América Latina já aparecem na página</t>
+  </si>
+  <si>
+    <t>E-E-A-T, América Latina, typos</t>
+  </si>
+  <si>
+    <t>Parágrafo de autoridade, América Latina e correção de "SAP BW/HANA"/"DAP BW" aplicados</t>
+  </si>
+  <si>
+    <t>Corpo do post</t>
+  </si>
+  <si>
+    <t>Páginas de solução</t>
+  </si>
+  <si>
+    <t>Titles em CAIXA ALTA</t>
+  </si>
+  <si>
+    <t>SAP BUSINESS DATA CLOUD, FÁBRICA DE BI, CONSOLIDAÇÃO CONTÁBIL etc. Usar caixa normal + keyword</t>
   </si>
   <si>
     <t>Sitemap</t>
@@ -534,34 +570,16 @@
     <t>/banner/banner-2, /banner/banner-3, /video-aceleradores/video-teste/, /midia-em-acelerador/analytics/, /cases-abertos/</t>
   </si>
   <si>
-    <t>Aplicado 25/09 por página (noindex). Falta marcar noindex no tipo de post inteiro (Banners, Mídias e Vídeos Aceleradores)</t>
-  </si>
-  <si>
-    <t>Fonte externa (Gartner/IDC)</t>
-  </si>
-  <si>
-    <t>Não confirmado na página atual</t>
-  </si>
-  <si>
-    <t>Elementor &gt; texto de contexto</t>
-  </si>
-  <si>
-    <t>A verificar</t>
-  </si>
-  <si>
-    <t>Prova social e América Latina</t>
-  </si>
-  <si>
-    <t>Gold, prêmio e América Latina já aparecem na página</t>
-  </si>
-  <si>
-    <t>E-E-A-T, América Latina, typos</t>
-  </si>
-  <si>
-    <t>Parágrafo de autoridade, América Latina e correção de "SAP BW/HANA"/"DAP BW" aplicados</t>
-  </si>
-  <si>
-    <t>Corpo do post</t>
+    <t>Feito 25/09: noindex por página + nos tipos Banners, Mídias e Vídeos Aceleradores (Rank Math &gt; Títulos e Meta). Saíram do sitemap</t>
+  </si>
+  <si>
+    <t>Contato, Sobre, Analytics, Blog, Serviços</t>
+  </si>
+  <si>
+    <t>Descriptions fracas ou duplicadas</t>
+  </si>
+  <si>
+    <t>"CONTATO", "Sobre Nós", "Analytics", Blog vazia; /servicos/ copia a description da BDC. Reescrever com 120-155 caracteres</t>
   </si>
   <si>
     <t>Blog (41 URLs)</t>
@@ -573,15 +591,6 @@
     <t>O sufixo " - Solveplan" estoura o limite. Aplicado 25/09 em 39 URLs (2 mantidos por decisão)</t>
   </si>
   <si>
-    <t>Contato, Sobre, Analytics, Blog, Serviços</t>
-  </si>
-  <si>
-    <t>Descriptions fracas ou duplicadas</t>
-  </si>
-  <si>
-    <t>"CONTATO", "Sobre Nós", "Analytics", Blog vazia; /servicos/ copia a description da BDC. Reescrever com 120-155 caracteres</t>
-  </si>
-  <si>
     <t>Post Clean Core</t>
   </si>
   <si>
@@ -589,15 +598,6 @@
   </si>
   <si>
     <t>Usa a description do post de agronegócio</t>
-  </si>
-  <si>
-    <t>Páginas de solução</t>
-  </si>
-  <si>
-    <t>Titles em CAIXA ALTA</t>
-  </si>
-  <si>
-    <t>SAP BUSINESS DATA CLOUD, FÁBRICA DE BI, CONSOLIDAÇÃO CONTÁBIL etc. Usar caixa normal + keyword</t>
   </si>
   <si>
     <t>4-Baixa</t>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A236C6D-D2B5-452C-8C3C-F12A92A083D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37F938A3-B3AD-4ACF-9FE1-1B1250A4C035}">
   <dimension ref="B1:E30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2430,12 +2430,12 @@
         <v>95</v>
       </c>
       <c r="C17" s="17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C18" s="17">
         <v>2</v>
@@ -2446,7 +2446,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
@@ -2568,7 +2568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBF1BF60-CF2F-4222-A046-DC50B3BFA3CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5F5EDEB-9EE9-4E70-9FF7-DF742F088782}">
   <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3228,10 +3228,10 @@
         <v>32</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>101</v>
@@ -3243,7 +3243,7 @@
         <v>103</v>
       </c>
       <c r="G21" s="9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>17</v>
@@ -3252,7 +3252,7 @@
         <v>18</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -3260,10 +3260,10 @@
         <v>32</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>104</v>
@@ -3272,10 +3272,10 @@
         <v>105</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G22" s="9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>17</v>
@@ -3284,7 +3284,7 @@
         <v>18</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3298,13 +3298,13 @@
         <v>49</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G23" s="9">
         <v>3</v>
@@ -3330,13 +3330,13 @@
         <v>49</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G24" s="9">
         <v>8</v>
@@ -3359,19 +3359,19 @@
         <v>72</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="G25" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>17</v>
@@ -3380,7 +3380,7 @@
         <v>18</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3388,22 +3388,22 @@
         <v>32</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="9">
-        <v>13</v>
+        <v>118</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>17</v>
@@ -3412,7 +3412,7 @@
         <v>18</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3420,22 +3420,22 @@
         <v>32</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="G27" s="9">
+        <v>13</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>17</v>
@@ -3444,10 +3444,10 @@
         <v>18</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
@@ -3455,7 +3455,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>79</v>
+        <v>12</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>124</v>
@@ -3479,7 +3479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>32</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>41</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>128</v>
@@ -3575,7 +3575,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>132</v>
       </c>
@@ -3583,22 +3583,22 @@
         <v>33</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="E32" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="F32" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>143</v>
-      </c>
       <c r="G32" s="9" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>39</v>
@@ -3612,34 +3612,34 @@
         <v>132</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="F33" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>148</v>
-      </c>
       <c r="G33" s="9" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>132</v>
       </c>
@@ -3650,16 +3650,16 @@
         <v>12</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>17</v>
@@ -3668,7 +3668,7 @@
         <v>39</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>19</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -3676,10 +3676,10 @@
         <v>132</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>12</v>
+        <v>153</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>154</v>
@@ -3703,36 +3703,36 @@
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>132</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C36" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="F36" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>127</v>
+      <c r="G36" s="9">
+        <v>1</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="12" t="s">
-        <v>95</v>
+      <c r="I36" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -3743,7 +3743,7 @@
         <v>87</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>163</v>
@@ -3752,22 +3752,22 @@
         <v>164</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="G37" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="13" t="s">
-        <v>166</v>
+      <c r="I37" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>132</v>
       </c>
@@ -3778,16 +3778,16 @@
         <v>97</v>
       </c>
       <c r="D38" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F38" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>103</v>
-      </c>
       <c r="G38" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H38" s="9" t="s">
         <v>17</v>
@@ -3804,10 +3804,10 @@
         <v>132</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>169</v>
@@ -3816,10 +3816,10 @@
         <v>170</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G39" s="9">
-        <v>6</v>
+        <v>130</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>131</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>17</v>
@@ -3828,10 +3828,10 @@
         <v>18</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>132</v>
       </c>
@@ -3839,19 +3839,19 @@
         <v>33</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D40" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="E40" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="F40" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F40" s="9" t="s">
-        <v>126</v>
-      </c>
       <c r="G40" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>17</v>
@@ -3880,10 +3880,10 @@
         <v>177</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>17</v>
@@ -3895,7 +3895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>132</v>
       </c>
@@ -3912,10 +3912,10 @@
         <v>180</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>17</v>
@@ -3927,7 +3927,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>132</v>
       </c>
@@ -3944,10 +3944,10 @@
         <v>183</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="H43" s="9" t="s">
         <v>17</v>
@@ -3999,7 +3999,7 @@
         <v>72</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>188</v>
@@ -4020,7 +4020,7 @@
         <v>39</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
@@ -4028,7 +4028,7 @@
         <v>184</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>12</v>
@@ -4043,7 +4043,7 @@
         <v>193</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="H46" s="9" t="s">
         <v>17</v>
@@ -4107,7 +4107,7 @@
         <v>201</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>17</v>
@@ -4127,7 +4127,7 @@
         <v>72</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>202</v>
@@ -4145,20 +4145,20 @@
         <v>17</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J49" xr:uid="{FBF1BF60-CF2F-4222-A046-DC50B3BFA3CF}"/>
+  <autoFilter ref="A1:J49" xr:uid="{A5F5EDEB-9EE9-4E70-9FF7-DF742F088782}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC969702-A1B1-42F2-A3CF-74794DB0AC20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F3D1E9-54C9-42A0-9AA5-0C3D505A53E4}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
         <v>214</v>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
         <v>215</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
         <v>216</v>
@@ -4331,7 +4331,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>217</v>
@@ -4510,7 +4510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995648DB-74D7-43ED-80E9-BBF3C5110EBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB5BB39E-9C16-4A02-8B6F-3E582936CF0C}">
   <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4549,10 +4549,10 @@
         <v>232</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>233</v>
@@ -7522,7 +7522,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K92" xr:uid="{995648DB-74D7-43ED-80E9-BBF3C5110EBC}"/>
+  <autoFilter ref="A1:K92" xr:uid="{AB5BB39E-9C16-4A02-8B6F-3E582936CF0C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>